--- a/research/traditional_assets/database/data/tanzania/tanzania_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_beverage_alcoholic.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1172620337865825</v>
+        <v>0.1169417476852228</v>
       </c>
       <c r="C2">
-        <v>1316.935734627333</v>
+        <v>1309.155438216345</v>
       </c>
       <c r="D2">
-        <v>1196.335734627334</v>
+        <v>1201.721738216345</v>
       </c>
       <c r="E2">
-        <v>-5.43</v>
+        <v>7.736300000000002</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.1663</v>
       </c>
       <c r="G2">
         <v>120.6</v>
@@ -1457,28 +1457,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.66226489</v>
       </c>
       <c r="N2">
-        <v>78.94489795918368</v>
+        <v>78.28263306918367</v>
       </c>
       <c r="O2">
-        <v>23.6834693877551</v>
+        <v>23.4847899207551</v>
       </c>
       <c r="P2">
-        <v>55.26142857142857</v>
+        <v>54.79784314842857</v>
       </c>
       <c r="Q2">
-        <v>88.56142857142856</v>
+        <v>88.09784314842857</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1172620337865825</v>
+        <v>0.1177673208941644</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6959789964029562</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.2044137492834</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1169417476852228</v>
+        <v>0.116621461583863</v>
       </c>
       <c r="C3">
-        <v>1309.155438216345</v>
+        <v>1301.423857605704</v>
       </c>
       <c r="D3">
-        <v>1201.721738216345</v>
+        <v>1207.156457605704</v>
       </c>
       <c r="E3">
-        <v>7.736300000000002</v>
+        <v>20.9026</v>
       </c>
       <c r="F3">
-        <v>13.1663</v>
+        <v>26.3326</v>
       </c>
       <c r="G3">
         <v>120.6</v>
@@ -1539,28 +1539,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M3">
-        <v>0.66226489</v>
+        <v>1.32452978</v>
       </c>
       <c r="N3">
-        <v>78.28263306918367</v>
+        <v>77.62036817918367</v>
       </c>
       <c r="O3">
-        <v>23.4847899207551</v>
+        <v>23.2861104537551</v>
       </c>
       <c r="P3">
-        <v>54.79784314842857</v>
+        <v>54.33425772542857</v>
       </c>
       <c r="Q3">
-        <v>88.09784314842857</v>
+        <v>87.63425772542857</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1177673208941644</v>
+        <v>0.1182829199835337</v>
       </c>
       <c r="T3">
-        <v>0.6959789964029562</v>
+        <v>0.7009652336604641</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.2044137492834</v>
+        <v>59.60220687464171</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.116621461583863</v>
+        <v>0.1163011754825033</v>
       </c>
       <c r="C4">
-        <v>1301.423857605704</v>
+        <v>1293.741656741522</v>
       </c>
       <c r="D4">
-        <v>1207.156457605704</v>
+        <v>1212.640556741522</v>
       </c>
       <c r="E4">
-        <v>20.9026</v>
+        <v>34.0689</v>
       </c>
       <c r="F4">
-        <v>26.3326</v>
+        <v>39.4989</v>
       </c>
       <c r="G4">
         <v>120.6</v>
@@ -1621,28 +1621,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M4">
-        <v>1.32452978</v>
+        <v>1.98679467</v>
       </c>
       <c r="N4">
-        <v>77.62036817918367</v>
+        <v>76.95810328918368</v>
       </c>
       <c r="O4">
-        <v>23.2861104537551</v>
+        <v>23.08743098675511</v>
       </c>
       <c r="P4">
-        <v>54.33425772542857</v>
+        <v>53.87067230242857</v>
       </c>
       <c r="Q4">
-        <v>87.63425772542857</v>
+        <v>87.17067230242857</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1182829199835337</v>
+        <v>0.1188091499819622</v>
       </c>
       <c r="T4">
-        <v>0.7009652336604641</v>
+        <v>0.7060542799335908</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.60220687464171</v>
+        <v>39.73480458309448</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1163011754825033</v>
+        <v>0.1159808893811435</v>
       </c>
       <c r="C5">
-        <v>1293.741656741522</v>
+        <v>1286.109511690174</v>
       </c>
       <c r="D5">
-        <v>1212.640556741522</v>
+        <v>1218.174711690174</v>
       </c>
       <c r="E5">
-        <v>34.0689</v>
+        <v>47.23520000000001</v>
       </c>
       <c r="F5">
-        <v>39.4989</v>
+        <v>52.66520000000001</v>
       </c>
       <c r="G5">
         <v>120.6</v>
@@ -1703,28 +1703,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M5">
-        <v>1.98679467</v>
+        <v>2.64905956</v>
       </c>
       <c r="N5">
-        <v>76.95810328918368</v>
+        <v>76.29583839918368</v>
       </c>
       <c r="O5">
-        <v>23.08743098675511</v>
+        <v>22.8887515197551</v>
       </c>
       <c r="P5">
-        <v>53.87067230242857</v>
+        <v>53.40708687942858</v>
       </c>
       <c r="Q5">
-        <v>87.17067230242857</v>
+        <v>86.70708687942857</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1188091499819622</v>
+        <v>0.1193463431053579</v>
       </c>
       <c r="T5">
-        <v>0.7060542799335908</v>
+        <v>0.7112493480040742</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.73480458309448</v>
+        <v>29.80110343732086</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1159808893811435</v>
+        <v>0.1156606032797838</v>
       </c>
       <c r="C6">
-        <v>1286.109511690174</v>
+        <v>1278.528110916133</v>
       </c>
       <c r="D6">
-        <v>1218.174711690174</v>
+        <v>1223.759610916133</v>
       </c>
       <c r="E6">
-        <v>47.23520000000001</v>
+        <v>60.40150000000001</v>
       </c>
       <c r="F6">
-        <v>52.66520000000001</v>
+        <v>65.83150000000001</v>
       </c>
       <c r="G6">
         <v>120.6</v>
@@ -1785,28 +1785,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M6">
-        <v>2.64905956</v>
+        <v>3.31132445</v>
       </c>
       <c r="N6">
-        <v>76.29583839918368</v>
+        <v>75.63357350918368</v>
       </c>
       <c r="O6">
-        <v>22.8887515197551</v>
+        <v>22.6900720527551</v>
       </c>
       <c r="P6">
-        <v>53.40708687942858</v>
+        <v>52.94350145642858</v>
       </c>
       <c r="Q6">
-        <v>86.70708687942857</v>
+        <v>86.24350145642858</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1193463431053579</v>
+        <v>0.1198948455576672</v>
       </c>
       <c r="T6">
-        <v>0.7112493480040742</v>
+        <v>0.7165537859286731</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.80110343732086</v>
+        <v>23.84088274985668</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1156606032797838</v>
+        <v>0.115340317178424</v>
       </c>
       <c r="C7">
-        <v>1278.528110916133</v>
+        <v>1270.998155567484</v>
       </c>
       <c r="D7">
-        <v>1223.759610916133</v>
+        <v>1229.395955567484</v>
       </c>
       <c r="E7">
-        <v>60.40150000000001</v>
+        <v>73.56780000000001</v>
       </c>
       <c r="F7">
-        <v>65.83150000000001</v>
+        <v>78.99780000000001</v>
       </c>
       <c r="G7">
         <v>120.6</v>
@@ -1867,28 +1867,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M7">
-        <v>3.31132445</v>
+        <v>3.973589340000001</v>
       </c>
       <c r="N7">
-        <v>75.63357350918368</v>
+        <v>74.97130861918367</v>
       </c>
       <c r="O7">
-        <v>22.6900720527551</v>
+        <v>22.4913925857551</v>
       </c>
       <c r="P7">
-        <v>52.94350145642858</v>
+        <v>52.47991603342857</v>
       </c>
       <c r="Q7">
-        <v>86.24350145642858</v>
+        <v>85.77991603342858</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1198948455576672</v>
+        <v>0.1204550182749192</v>
       </c>
       <c r="T7">
-        <v>0.7165537859286731</v>
+        <v>0.7219710842346465</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.84088274985668</v>
+        <v>19.86740229154723</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.115340317178424</v>
+        <v>0.1150200310770643</v>
       </c>
       <c r="C8">
-        <v>1270.998155567484</v>
+        <v>1263.520359769364</v>
       </c>
       <c r="D8">
-        <v>1229.395955567484</v>
+        <v>1235.084459769364</v>
       </c>
       <c r="E8">
-        <v>73.56780000000001</v>
+        <v>86.73410000000001</v>
       </c>
       <c r="F8">
-        <v>78.9978</v>
+        <v>92.1641</v>
       </c>
       <c r="G8">
         <v>120.6</v>
@@ -1949,28 +1949,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M8">
-        <v>3.97358934</v>
+        <v>4.63585423</v>
       </c>
       <c r="N8">
-        <v>74.97130861918367</v>
+        <v>74.30904372918368</v>
       </c>
       <c r="O8">
-        <v>22.4913925857551</v>
+        <v>22.29271311875511</v>
       </c>
       <c r="P8">
-        <v>52.47991603342857</v>
+        <v>52.01633061042858</v>
       </c>
       <c r="Q8">
-        <v>85.77991603342858</v>
+        <v>85.31633061042858</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1204550182749192</v>
+        <v>0.1210272377172734</v>
       </c>
       <c r="T8">
-        <v>0.7219710842346465</v>
+        <v>0.7275048835794581</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.86740229154724</v>
+        <v>17.02920196418335</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1150200310770643</v>
+        <v>0.1146997449757046</v>
       </c>
       <c r="C9">
-        <v>1263.520359769364</v>
+        <v>1256.095450925587</v>
       </c>
       <c r="D9">
-        <v>1235.084459769364</v>
+        <v>1240.825850925587</v>
       </c>
       <c r="E9">
-        <v>86.73410000000001</v>
+        <v>99.90040000000002</v>
       </c>
       <c r="F9">
-        <v>92.16410000000002</v>
+        <v>105.3304</v>
       </c>
       <c r="G9">
         <v>120.6</v>
@@ -2031,28 +2031,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M9">
-        <v>4.635854230000001</v>
+        <v>5.29811912</v>
       </c>
       <c r="N9">
-        <v>74.30904372918367</v>
+        <v>73.64677883918368</v>
       </c>
       <c r="O9">
-        <v>22.2927131187551</v>
+        <v>22.0940336517551</v>
       </c>
       <c r="P9">
-        <v>52.01633061042857</v>
+        <v>51.55274518742858</v>
       </c>
       <c r="Q9">
-        <v>85.31633061042857</v>
+        <v>84.85274518742858</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1210272377172734</v>
+        <v>0.1216118967127224</v>
       </c>
       <c r="T9">
-        <v>0.7275048835794581</v>
+        <v>0.7331589829100263</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.02920196418334</v>
+        <v>14.90055171866043</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1146997449757046</v>
+        <v>0.1143794588743448</v>
       </c>
       <c r="C10">
-        <v>1256.095450925587</v>
+        <v>1248.72417002872</v>
       </c>
       <c r="D10">
-        <v>1240.825850925587</v>
+        <v>1246.62087002872</v>
       </c>
       <c r="E10">
-        <v>99.90040000000002</v>
+        <v>113.0667</v>
       </c>
       <c r="F10">
-        <v>105.3304</v>
+        <v>118.4967</v>
       </c>
       <c r="G10">
         <v>120.6</v>
@@ -2113,28 +2113,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M10">
-        <v>5.29811912</v>
+        <v>5.96038401</v>
       </c>
       <c r="N10">
-        <v>73.64677883918368</v>
+        <v>72.98451394918368</v>
       </c>
       <c r="O10">
-        <v>22.0940336517551</v>
+        <v>21.8953541847551</v>
       </c>
       <c r="P10">
-        <v>51.55274518742858</v>
+        <v>51.08915976442857</v>
       </c>
       <c r="Q10">
-        <v>84.85274518742858</v>
+        <v>84.38915976442857</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1216118967127224</v>
+        <v>0.1222094053564229</v>
       </c>
       <c r="T10">
-        <v>0.7331589829100263</v>
+        <v>0.7389373481599476</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.90055171866043</v>
+        <v>13.24493486103149</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1143794588743448</v>
+        <v>0.1141641727729851</v>
       </c>
       <c r="C11">
-        <v>1248.72417002872</v>
+        <v>1239.483612652322</v>
       </c>
       <c r="D11">
-        <v>1246.62087002872</v>
+        <v>1250.546612652322</v>
       </c>
       <c r="E11">
-        <v>113.0667</v>
+        <v>126.233</v>
       </c>
       <c r="F11">
-        <v>118.4967</v>
+        <v>131.663</v>
       </c>
       <c r="G11">
         <v>120.6</v>
@@ -2195,45 +2195,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M11">
-        <v>5.96038401</v>
+        <v>6.8201434</v>
       </c>
       <c r="N11">
-        <v>72.98451394918368</v>
+        <v>72.12475455918367</v>
       </c>
       <c r="O11">
-        <v>21.8953541847551</v>
+        <v>21.6374263677551</v>
       </c>
       <c r="P11">
-        <v>51.08915976442857</v>
+        <v>50.48732819142857</v>
       </c>
       <c r="Q11">
-        <v>84.38915976442857</v>
+        <v>83.78732819142857</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1222094053564229</v>
+        <v>0.1228201919699834</v>
       </c>
       <c r="T11">
-        <v>0.7389373481599476</v>
+        <v>0.7448441215265339</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.24493486103149</v>
+        <v>11.57525484862733</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1141641727729851</v>
+        <v>0.1138543866716253</v>
       </c>
       <c r="C12">
-        <v>1239.483612652322</v>
+        <v>1232.009847382984</v>
       </c>
       <c r="D12">
-        <v>1250.546612652322</v>
+        <v>1256.239147382984</v>
       </c>
       <c r="E12">
-        <v>126.233</v>
+        <v>139.3993</v>
       </c>
       <c r="F12">
-        <v>131.663</v>
+        <v>144.8293</v>
       </c>
       <c r="G12">
         <v>120.6</v>
@@ -2277,28 +2277,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M12">
-        <v>6.8201434</v>
+        <v>7.50215774</v>
       </c>
       <c r="N12">
-        <v>72.12475455918367</v>
+        <v>71.44274021918368</v>
       </c>
       <c r="O12">
-        <v>21.6374263677551</v>
+        <v>21.4328220657551</v>
       </c>
       <c r="P12">
-        <v>50.48732819142857</v>
+        <v>50.00991815342857</v>
       </c>
       <c r="Q12">
-        <v>83.78732819142857</v>
+        <v>83.30991815342857</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1228201919699834</v>
+        <v>0.1234447041254217</v>
       </c>
       <c r="T12">
-        <v>0.7448441215265339</v>
+        <v>0.7508836313732683</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.57525484862733</v>
+        <v>10.52295895329757</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1138543866716253</v>
+        <v>0.1136874005702656</v>
       </c>
       <c r="C13">
-        <v>1232.009847382984</v>
+        <v>1221.933582880512</v>
       </c>
       <c r="D13">
-        <v>1256.239147382984</v>
+        <v>1259.329182880512</v>
       </c>
       <c r="E13">
-        <v>139.3993</v>
+        <v>152.5656</v>
       </c>
       <c r="F13">
-        <v>144.8293</v>
+        <v>157.9956</v>
       </c>
       <c r="G13">
         <v>120.6</v>
@@ -2359,45 +2359,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M13">
-        <v>7.50215774</v>
+        <v>8.4527646</v>
       </c>
       <c r="N13">
-        <v>71.44274021918368</v>
+        <v>70.49213335918368</v>
       </c>
       <c r="O13">
-        <v>21.4328220657551</v>
+        <v>21.1476400077551</v>
       </c>
       <c r="P13">
-        <v>50.00991815342857</v>
+        <v>49.34449335142858</v>
       </c>
       <c r="Q13">
-        <v>83.30991815342857</v>
+        <v>82.64449335142858</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1234447041254217</v>
+        <v>0.1240834097389381</v>
       </c>
       <c r="T13">
-        <v>0.7508836313732683</v>
+        <v>0.7570604028074284</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.52295895329757</v>
+        <v>9.339535843596506</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1136874005702656</v>
+        <v>0.1133895144689058</v>
       </c>
       <c r="C14">
-        <v>1221.933582880512</v>
+        <v>1214.317502667775</v>
       </c>
       <c r="D14">
-        <v>1259.329182880512</v>
+        <v>1264.879402667775</v>
       </c>
       <c r="E14">
-        <v>152.5656</v>
+        <v>165.7319</v>
       </c>
       <c r="F14">
-        <v>157.9956</v>
+        <v>171.1619</v>
       </c>
       <c r="G14">
         <v>120.6</v>
@@ -2441,28 +2441,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M14">
-        <v>8.4527646</v>
+        <v>9.157161650000001</v>
       </c>
       <c r="N14">
-        <v>70.49213335918368</v>
+        <v>69.78773630918367</v>
       </c>
       <c r="O14">
-        <v>21.1476400077551</v>
+        <v>20.9363208927551</v>
       </c>
       <c r="P14">
-        <v>49.34449335142858</v>
+        <v>48.85141541642857</v>
       </c>
       <c r="Q14">
-        <v>82.64449335142858</v>
+        <v>82.15141541642856</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1240834097389381</v>
+        <v>0.1247367982401216</v>
       </c>
       <c r="T14">
-        <v>0.7570604028074284</v>
+        <v>0.7633791689872014</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.339535843596506</v>
+        <v>8.621110009473696</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1133895144689058</v>
+        <v>0.1130916283675461</v>
       </c>
       <c r="C15">
-        <v>1214.317502667775</v>
+        <v>1206.750561801915</v>
       </c>
       <c r="D15">
-        <v>1264.879402667775</v>
+        <v>1270.478761801915</v>
       </c>
       <c r="E15">
-        <v>165.7319</v>
+        <v>178.8982</v>
       </c>
       <c r="F15">
-        <v>171.1619</v>
+        <v>184.3282</v>
       </c>
       <c r="G15">
         <v>120.6</v>
@@ -2523,28 +2523,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M15">
-        <v>9.157161650000001</v>
+        <v>9.861558700000002</v>
       </c>
       <c r="N15">
-        <v>69.78773630918367</v>
+        <v>69.08333925918367</v>
       </c>
       <c r="O15">
-        <v>20.9363208927551</v>
+        <v>20.7250017777551</v>
       </c>
       <c r="P15">
-        <v>48.85141541642857</v>
+        <v>48.35833748142858</v>
       </c>
       <c r="Q15">
-        <v>82.15141541642856</v>
+        <v>81.65833748142857</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1247367982401216</v>
+        <v>0.125405381822728</v>
       </c>
       <c r="T15">
-        <v>0.7633791689872014</v>
+        <v>0.7698448832176666</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.621110009473696</v>
+        <v>8.005316437368432</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1130916283675461</v>
+        <v>0.1128777422661863</v>
       </c>
       <c r="C16">
-        <v>1206.750561801915</v>
+        <v>1197.63534849687</v>
       </c>
       <c r="D16">
-        <v>1270.478761801915</v>
+        <v>1274.52984849687</v>
       </c>
       <c r="E16">
-        <v>178.8982</v>
+        <v>192.0645</v>
       </c>
       <c r="F16">
-        <v>184.3282</v>
+        <v>197.4945</v>
       </c>
       <c r="G16">
         <v>120.6</v>
@@ -2605,45 +2605,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M16">
-        <v>9.861558700000002</v>
+        <v>10.72395135</v>
       </c>
       <c r="N16">
-        <v>69.08333925918367</v>
+        <v>68.22094660918367</v>
       </c>
       <c r="O16">
-        <v>20.7250017777551</v>
+        <v>20.4662839827551</v>
       </c>
       <c r="P16">
-        <v>48.35833748142858</v>
+        <v>47.75466262642857</v>
       </c>
       <c r="Q16">
-        <v>81.65833748142857</v>
+        <v>81.05466262642857</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.125405381822728</v>
+        <v>0.1260896967837486</v>
       </c>
       <c r="T16">
-        <v>0.7698448832176666</v>
+        <v>0.7764627319006137</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.005316437368432</v>
+        <v>7.361549431048441</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1128777422661863</v>
+        <v>0.1125854561648266</v>
       </c>
       <c r="C17">
-        <v>1197.63534849687</v>
+        <v>1190.047019837881</v>
       </c>
       <c r="D17">
-        <v>1274.52984849687</v>
+        <v>1280.107819837881</v>
       </c>
       <c r="E17">
-        <v>192.0645</v>
+        <v>205.2308</v>
       </c>
       <c r="F17">
-        <v>197.4945</v>
+        <v>210.6608</v>
       </c>
       <c r="G17">
         <v>120.6</v>
@@ -2687,28 +2687,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M17">
-        <v>10.72395135</v>
+        <v>11.43888144</v>
       </c>
       <c r="N17">
-        <v>68.22094660918367</v>
+        <v>67.50601651918367</v>
       </c>
       <c r="O17">
-        <v>20.4662839827551</v>
+        <v>20.2518049557551</v>
       </c>
       <c r="P17">
-        <v>47.75466262642857</v>
+        <v>47.25421156342857</v>
       </c>
       <c r="Q17">
-        <v>81.05466262642857</v>
+        <v>80.55421156342857</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1260896967837486</v>
+        <v>0.1267903049581269</v>
       </c>
       <c r="T17">
-        <v>0.7764627319006137</v>
+        <v>0.7832381484093449</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.361549431048441</v>
+        <v>6.901452591607914</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1125854561648266</v>
+        <v>0.1122931700634668</v>
       </c>
       <c r="C18">
-        <v>1190.047019837881</v>
+        <v>1182.507729704058</v>
       </c>
       <c r="D18">
-        <v>1280.107819837881</v>
+        <v>1285.734829704058</v>
       </c>
       <c r="E18">
-        <v>205.2308</v>
+        <v>218.3971</v>
       </c>
       <c r="F18">
-        <v>210.6608</v>
+        <v>223.8271</v>
       </c>
       <c r="G18">
         <v>120.6</v>
@@ -2769,28 +2769,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M18">
-        <v>11.43888144</v>
+        <v>12.15381153</v>
       </c>
       <c r="N18">
-        <v>67.50601651918367</v>
+        <v>66.79108642918368</v>
       </c>
       <c r="O18">
-        <v>20.2518049557551</v>
+        <v>20.0373259287551</v>
       </c>
       <c r="P18">
-        <v>47.25421156342857</v>
+        <v>46.75376050042858</v>
       </c>
       <c r="Q18">
-        <v>80.55421156342857</v>
+        <v>80.05376050042858</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1267903049581269</v>
+        <v>0.127507795257189</v>
       </c>
       <c r="T18">
-        <v>0.7832381484093449</v>
+        <v>0.7901768279664796</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.901452591607914</v>
+        <v>6.495484792101566</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1122931700634668</v>
+        <v>0.1120008839621071</v>
       </c>
       <c r="C19">
-        <v>1182.507729704058</v>
+        <v>1175.01812763111</v>
       </c>
       <c r="D19">
-        <v>1285.734829704058</v>
+        <v>1291.41152763111</v>
       </c>
       <c r="E19">
-        <v>218.3971</v>
+        <v>231.5634</v>
       </c>
       <c r="F19">
-        <v>223.8271</v>
+        <v>236.9934</v>
       </c>
       <c r="G19">
         <v>120.6</v>
@@ -2851,28 +2851,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M19">
-        <v>12.15381153</v>
+        <v>12.86874162</v>
       </c>
       <c r="N19">
-        <v>66.79108642918368</v>
+        <v>66.07615633918368</v>
       </c>
       <c r="O19">
-        <v>20.0373259287551</v>
+        <v>19.8228469017551</v>
       </c>
       <c r="P19">
-        <v>46.75376050042858</v>
+        <v>46.25330943742858</v>
       </c>
       <c r="Q19">
-        <v>80.05376050042858</v>
+        <v>79.55330943742858</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.127507795257189</v>
+        <v>0.1282427853196428</v>
       </c>
       <c r="T19">
-        <v>0.7901768279664796</v>
+        <v>0.7972847436103734</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.495484792101566</v>
+        <v>6.134624525873702</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1120008839621071</v>
+        <v>0.1118415978607473</v>
       </c>
       <c r="C20">
-        <v>1175.01812763111</v>
+        <v>1164.966590358703</v>
       </c>
       <c r="D20">
-        <v>1291.41152763111</v>
+        <v>1294.526290358703</v>
       </c>
       <c r="E20">
-        <v>231.5634</v>
+        <v>244.7297</v>
       </c>
       <c r="F20">
-        <v>236.9934</v>
+        <v>250.1597</v>
       </c>
       <c r="G20">
         <v>120.6</v>
@@ -2933,45 +2933,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M20">
-        <v>12.86874162</v>
+        <v>13.83383141</v>
       </c>
       <c r="N20">
-        <v>66.07615633918368</v>
+        <v>65.11106654918368</v>
       </c>
       <c r="O20">
-        <v>19.8228469017551</v>
+        <v>19.5333199647551</v>
       </c>
       <c r="P20">
-        <v>46.25330943742858</v>
+        <v>45.57774658442857</v>
       </c>
       <c r="Q20">
-        <v>79.55330943742858</v>
+        <v>78.87774658442856</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1282427853196428</v>
+        <v>0.1289959232848732</v>
       </c>
       <c r="T20">
-        <v>0.7972847436103734</v>
+        <v>0.80456816334424</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.134624525873702</v>
+        <v>5.706654622241321</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1118415978607473</v>
+        <v>0.1115563117593876</v>
       </c>
       <c r="C21">
-        <v>1164.966590358703</v>
+        <v>1157.416638791314</v>
       </c>
       <c r="D21">
-        <v>1294.526290358703</v>
+        <v>1300.142638791315</v>
       </c>
       <c r="E21">
-        <v>244.7297</v>
+        <v>257.896</v>
       </c>
       <c r="F21">
-        <v>250.1597</v>
+        <v>263.326</v>
       </c>
       <c r="G21">
         <v>120.6</v>
@@ -3015,28 +3015,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M21">
-        <v>13.83383141</v>
+        <v>14.5619278</v>
       </c>
       <c r="N21">
-        <v>65.11106654918368</v>
+        <v>64.38297015918367</v>
       </c>
       <c r="O21">
-        <v>19.5333199647551</v>
+        <v>19.3148910477551</v>
       </c>
       <c r="P21">
-        <v>45.57774658442857</v>
+        <v>45.06807911142857</v>
       </c>
       <c r="Q21">
-        <v>78.87774658442856</v>
+        <v>78.36807911142857</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1289959232848732</v>
+        <v>0.1297678896992345</v>
       </c>
       <c r="T21">
-        <v>0.80456816334424</v>
+        <v>0.8120336685714533</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.706654622241321</v>
+        <v>5.421321891129255</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1115563117593876</v>
+        <v>0.1112710256580279</v>
       </c>
       <c r="C22">
-        <v>1157.416638791314</v>
+        <v>1149.915633032613</v>
       </c>
       <c r="D22">
-        <v>1300.142638791315</v>
+        <v>1305.807933032613</v>
       </c>
       <c r="E22">
-        <v>257.896</v>
+        <v>271.0623000000001</v>
       </c>
       <c r="F22">
-        <v>263.326</v>
+        <v>276.4923000000001</v>
       </c>
       <c r="G22">
         <v>120.6</v>
@@ -3097,28 +3097,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M22">
-        <v>14.5619278</v>
+        <v>15.29002419</v>
       </c>
       <c r="N22">
-        <v>64.38297015918367</v>
+        <v>63.65487376918367</v>
       </c>
       <c r="O22">
-        <v>19.3148910477551</v>
+        <v>19.0964621307551</v>
       </c>
       <c r="P22">
-        <v>45.06807911142857</v>
+        <v>44.55841163842857</v>
       </c>
       <c r="Q22">
-        <v>78.36807911142857</v>
+        <v>77.85841163842858</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1297678896992345</v>
+        <v>0.1305593995671239</v>
       </c>
       <c r="T22">
-        <v>0.8120336685714533</v>
+        <v>0.8196881739310011</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.421321891129255</v>
+        <v>5.163163705837385</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1112710256580278</v>
+        <v>0.1109857395566681</v>
       </c>
       <c r="C23">
-        <v>1149.915633032613</v>
+        <v>1142.464215718199</v>
       </c>
       <c r="D23">
-        <v>1305.807933032613</v>
+        <v>1311.522815718199</v>
       </c>
       <c r="E23">
-        <v>271.0623</v>
+        <v>284.2286</v>
       </c>
       <c r="F23">
-        <v>276.4923</v>
+        <v>289.6586</v>
       </c>
       <c r="G23">
         <v>120.6</v>
@@ -3179,28 +3179,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M23">
-        <v>15.29002419</v>
+        <v>16.01812058</v>
       </c>
       <c r="N23">
-        <v>63.65487376918368</v>
+        <v>62.92677737918368</v>
       </c>
       <c r="O23">
-        <v>19.0964621307551</v>
+        <v>18.8780332137551</v>
       </c>
       <c r="P23">
-        <v>44.55841163842858</v>
+        <v>44.04874416542857</v>
       </c>
       <c r="Q23">
-        <v>77.85841163842858</v>
+        <v>77.34874416542857</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1305593995671238</v>
+        <v>0.1313712045598309</v>
       </c>
       <c r="T23">
-        <v>0.8196881739310009</v>
+        <v>0.8275389486587423</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.163163705837386</v>
+        <v>4.928474446481141</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1109857395566681</v>
+        <v>0.1107004534553083</v>
       </c>
       <c r="C24">
-        <v>1142.464215718199</v>
+        <v>1135.063040783131</v>
       </c>
       <c r="D24">
-        <v>1311.522815718199</v>
+        <v>1317.287940783131</v>
       </c>
       <c r="E24">
-        <v>284.2286</v>
+        <v>297.3949</v>
       </c>
       <c r="F24">
-        <v>289.6586</v>
+        <v>302.8249</v>
       </c>
       <c r="G24">
         <v>120.6</v>
@@ -3261,28 +3261,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M24">
-        <v>16.01812058</v>
+        <v>16.74621697</v>
       </c>
       <c r="N24">
-        <v>62.92677737918368</v>
+        <v>62.19868098918367</v>
       </c>
       <c r="O24">
-        <v>18.8780332137551</v>
+        <v>18.6596042967551</v>
       </c>
       <c r="P24">
-        <v>44.04874416542857</v>
+        <v>43.53907669242857</v>
       </c>
       <c r="Q24">
-        <v>77.34874416542857</v>
+        <v>76.83907669242856</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1313712045598309</v>
+        <v>0.1322040953965043</v>
       </c>
       <c r="T24">
-        <v>0.8275389486587423</v>
+        <v>0.8355936396131781</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.928474446481141</v>
+        <v>4.714192948808048</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1107004534553083</v>
+        <v>0.1104151673539486</v>
       </c>
       <c r="C25">
-        <v>1135.063040783131</v>
+        <v>1127.712773711369</v>
       </c>
       <c r="D25">
-        <v>1317.287940783131</v>
+        <v>1323.103973711369</v>
       </c>
       <c r="E25">
-        <v>297.3949</v>
+        <v>310.5612</v>
       </c>
       <c r="F25">
-        <v>302.8249</v>
+        <v>315.9912</v>
       </c>
       <c r="G25">
         <v>120.6</v>
@@ -3343,28 +3343,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M25">
-        <v>16.74621697</v>
+        <v>17.47431336</v>
       </c>
       <c r="N25">
-        <v>62.19868098918367</v>
+        <v>61.47058459918367</v>
       </c>
       <c r="O25">
-        <v>18.6596042967551</v>
+        <v>18.4411753797551</v>
       </c>
       <c r="P25">
-        <v>43.53907669242857</v>
+        <v>43.02940921942857</v>
       </c>
       <c r="Q25">
-        <v>76.83907669242856</v>
+        <v>76.32940921942857</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1322040953965043</v>
+        <v>0.1330589044130903</v>
       </c>
       <c r="T25">
-        <v>0.8355936396131781</v>
+        <v>0.8438602961190467</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.714192948808048</v>
+        <v>4.517768242607712</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1104151673539486</v>
+        <v>0.1105673812525888</v>
       </c>
       <c r="C26">
-        <v>1127.712773711369</v>
+        <v>1111.436963796809</v>
       </c>
       <c r="D26">
-        <v>1323.103973711369</v>
+        <v>1319.994463796809</v>
       </c>
       <c r="E26">
-        <v>310.5612</v>
+        <v>323.7275</v>
       </c>
       <c r="F26">
-        <v>315.9912</v>
+        <v>329.1575</v>
       </c>
       <c r="G26">
         <v>120.6</v>
@@ -3425,45 +3425,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M26">
-        <v>17.47431336</v>
+        <v>19.0253035</v>
       </c>
       <c r="N26">
-        <v>61.47058459918368</v>
+        <v>59.91959445918367</v>
       </c>
       <c r="O26">
-        <v>18.44117537975511</v>
+        <v>17.9758783377551</v>
       </c>
       <c r="P26">
-        <v>43.02940921942857</v>
+        <v>41.94371612142857</v>
       </c>
       <c r="Q26">
-        <v>76.32940921942857</v>
+        <v>75.24371612142856</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1330589044130903</v>
+        <v>0.1339365083367851</v>
       </c>
       <c r="T26">
-        <v>0.8438602961190467</v>
+        <v>0.8523473967984049</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.517768242607713</v>
+        <v>4.149468520130765</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1105673812525888</v>
+        <v>0.1109365951512291</v>
       </c>
       <c r="C27">
-        <v>1111.436963796809</v>
+        <v>1090.788536414645</v>
       </c>
       <c r="D27">
-        <v>1319.994463796809</v>
+        <v>1312.512336414645</v>
       </c>
       <c r="E27">
-        <v>323.7275</v>
+        <v>336.8938000000001</v>
       </c>
       <c r="F27">
-        <v>329.1575</v>
+        <v>342.3238000000001</v>
       </c>
       <c r="G27">
         <v>120.6</v>
@@ -3507,45 +3507,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M27">
-        <v>19.0253035</v>
+        <v>20.98444894</v>
       </c>
       <c r="N27">
-        <v>59.91959445918367</v>
+        <v>57.96044901918367</v>
       </c>
       <c r="O27">
-        <v>17.9758783377551</v>
+        <v>17.3881347057551</v>
       </c>
       <c r="P27">
-        <v>41.94371612142857</v>
+        <v>40.57231431342857</v>
       </c>
       <c r="Q27">
-        <v>75.24371612142856</v>
+        <v>73.87231431342857</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1339365083367851</v>
+        <v>0.1348378312854447</v>
       </c>
       <c r="T27">
-        <v>0.8523473967984049</v>
+        <v>0.8610638785772051</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.149468520130765</v>
+        <v>3.762066765961197</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1109365951512291</v>
+        <v>0.1106933090498694</v>
       </c>
       <c r="C28">
-        <v>1090.788536414645</v>
+        <v>1082.542867123544</v>
       </c>
       <c r="D28">
-        <v>1312.512336414645</v>
+        <v>1317.432967123544</v>
       </c>
       <c r="E28">
-        <v>336.8938000000001</v>
+        <v>350.0601</v>
       </c>
       <c r="F28">
-        <v>342.3238000000001</v>
+        <v>355.4901</v>
       </c>
       <c r="G28">
         <v>120.6</v>
@@ -3589,28 +3589,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M28">
-        <v>20.98444894</v>
+        <v>21.79154313</v>
       </c>
       <c r="N28">
-        <v>57.96044901918367</v>
+        <v>57.15335482918368</v>
       </c>
       <c r="O28">
-        <v>17.3881347057551</v>
+        <v>17.1460064487551</v>
       </c>
       <c r="P28">
-        <v>40.57231431342857</v>
+        <v>40.00734838042857</v>
       </c>
       <c r="Q28">
-        <v>73.87231431342857</v>
+        <v>73.30734838042858</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1348378312854447</v>
+        <v>0.1357638480135197</v>
       </c>
       <c r="T28">
-        <v>0.8610638785772051</v>
+        <v>0.8700191680759727</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.762066765961197</v>
+        <v>3.622730959814486</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1106933090498694</v>
+        <v>0.1109988229485096</v>
       </c>
       <c r="C29">
-        <v>1082.542867123544</v>
+        <v>1063.203233560437</v>
       </c>
       <c r="D29">
-        <v>1317.432967123544</v>
+        <v>1311.259633560437</v>
       </c>
       <c r="E29">
-        <v>350.0601</v>
+        <v>363.2264000000001</v>
       </c>
       <c r="F29">
-        <v>355.4901</v>
+        <v>368.6564000000001</v>
       </c>
       <c r="G29">
         <v>120.6</v>
@@ -3671,45 +3671,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M29">
-        <v>21.79154313</v>
+        <v>23.63087524000001</v>
       </c>
       <c r="N29">
-        <v>57.15335482918368</v>
+        <v>55.31402271918367</v>
       </c>
       <c r="O29">
-        <v>17.1460064487551</v>
+        <v>16.5942068157551</v>
       </c>
       <c r="P29">
-        <v>40.00734838042857</v>
+        <v>38.71981590342857</v>
       </c>
       <c r="Q29">
-        <v>73.30734838042858</v>
+        <v>72.01981590342857</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1357638480135197</v>
+        <v>0.1367155874284856</v>
       </c>
       <c r="T29">
-        <v>0.8700191680759727</v>
+        <v>0.8792232156163725</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.622730959814486</v>
+        <v>3.340752179401022</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1109988229485096</v>
+        <v>0.1107751368471499</v>
       </c>
       <c r="C30">
-        <v>1063.203233560437</v>
+        <v>1054.551130367618</v>
       </c>
       <c r="D30">
-        <v>1311.259633560437</v>
+        <v>1315.773830367618</v>
       </c>
       <c r="E30">
-        <v>363.2264000000001</v>
+        <v>376.3927</v>
       </c>
       <c r="F30">
-        <v>368.6564000000001</v>
+        <v>381.8227000000001</v>
       </c>
       <c r="G30">
         <v>120.6</v>
@@ -3753,28 +3753,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M30">
-        <v>23.63087524000001</v>
+        <v>24.47483507</v>
       </c>
       <c r="N30">
-        <v>55.31402271918367</v>
+        <v>54.47006288918367</v>
       </c>
       <c r="O30">
-        <v>16.5942068157551</v>
+        <v>16.3410188667551</v>
       </c>
       <c r="P30">
-        <v>38.71981590342857</v>
+        <v>38.12904402242857</v>
       </c>
       <c r="Q30">
-        <v>72.01981590342857</v>
+        <v>71.42904402242857</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1367155874284856</v>
+        <v>0.1376941364044364</v>
       </c>
       <c r="T30">
-        <v>0.8792232156163725</v>
+        <v>0.8886865321015726</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.340752179401022</v>
+        <v>3.225553828387194</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1107751368471499</v>
+        <v>0.1105514507457901</v>
       </c>
       <c r="C31">
-        <v>1054.551130367618</v>
+        <v>1045.930216069347</v>
       </c>
       <c r="D31">
-        <v>1315.773830367618</v>
+        <v>1320.319216069347</v>
       </c>
       <c r="E31">
-        <v>376.3927</v>
+        <v>389.559</v>
       </c>
       <c r="F31">
-        <v>381.8227</v>
+        <v>394.989</v>
       </c>
       <c r="G31">
         <v>120.6</v>
@@ -3835,28 +3835,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M31">
-        <v>24.47483507</v>
+        <v>25.3187949</v>
       </c>
       <c r="N31">
-        <v>54.47006288918368</v>
+        <v>53.62610305918368</v>
       </c>
       <c r="O31">
-        <v>16.3410188667551</v>
+        <v>16.0878309177551</v>
       </c>
       <c r="P31">
-        <v>38.12904402242857</v>
+        <v>37.53827214142858</v>
       </c>
       <c r="Q31">
-        <v>71.42904402242857</v>
+        <v>70.83827214142858</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1376941364044364</v>
+        <v>0.1387006439225573</v>
       </c>
       <c r="T31">
-        <v>0.8886865321015726</v>
+        <v>0.8984202290577781</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.225553828387195</v>
+        <v>3.118035367440954</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1105514507457901</v>
+        <v>0.1103277646444304</v>
       </c>
       <c r="C32">
-        <v>1045.930216069347</v>
+        <v>1037.34081501541</v>
       </c>
       <c r="D32">
-        <v>1320.319216069347</v>
+        <v>1324.896115015411</v>
       </c>
       <c r="E32">
-        <v>389.559</v>
+        <v>402.7253</v>
       </c>
       <c r="F32">
-        <v>394.989</v>
+        <v>408.1553</v>
       </c>
       <c r="G32">
         <v>120.6</v>
@@ -3917,28 +3917,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M32">
-        <v>25.3187949</v>
+        <v>26.16275473</v>
       </c>
       <c r="N32">
-        <v>53.62610305918368</v>
+        <v>52.78214322918367</v>
       </c>
       <c r="O32">
-        <v>16.0878309177551</v>
+        <v>15.8346429687551</v>
       </c>
       <c r="P32">
-        <v>37.53827214142858</v>
+        <v>36.94750026042857</v>
       </c>
       <c r="Q32">
-        <v>70.83827214142858</v>
+        <v>70.24750026042857</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1387006439225573</v>
+        <v>0.1397363255716382</v>
       </c>
       <c r="T32">
-        <v>0.8984202290577781</v>
+        <v>0.9084360621576417</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.118035367440954</v>
+        <v>3.017453581394472</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1103277646444304</v>
+        <v>0.1118512785430706</v>
       </c>
       <c r="C33">
-        <v>1037.34081501541</v>
+        <v>993.6149605298115</v>
       </c>
       <c r="D33">
-        <v>1324.896115015411</v>
+        <v>1294.336560529812</v>
       </c>
       <c r="E33">
-        <v>402.7253</v>
+        <v>415.8916</v>
       </c>
       <c r="F33">
-        <v>408.1553</v>
+        <v>421.3216</v>
       </c>
       <c r="G33">
         <v>120.6</v>
@@ -3999,45 +3999,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M33">
-        <v>26.16275473</v>
+        <v>30.29302304</v>
       </c>
       <c r="N33">
-        <v>52.78214322918367</v>
+        <v>48.65187491918367</v>
       </c>
       <c r="O33">
-        <v>15.8346429687551</v>
+        <v>14.5955624757551</v>
       </c>
       <c r="P33">
-        <v>36.94750026042857</v>
+        <v>34.05631244342857</v>
       </c>
       <c r="Q33">
-        <v>70.24750026042857</v>
+        <v>67.35631244342856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1397363255716382</v>
+        <v>0.1408024684456921</v>
       </c>
       <c r="T33">
-        <v>0.9084360621576417</v>
+        <v>0.9187464785839721</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.017453581394472</v>
+        <v>2.606042251212168</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1118512785430706</v>
+        <v>0.1116821924417109</v>
       </c>
       <c r="C34">
-        <v>993.6149605298115</v>
+        <v>983.7705645945705</v>
       </c>
       <c r="D34">
-        <v>1294.336560529812</v>
+        <v>1297.658464594571</v>
       </c>
       <c r="E34">
-        <v>415.8916</v>
+        <v>429.0579000000001</v>
       </c>
       <c r="F34">
-        <v>421.3216</v>
+        <v>434.4879000000001</v>
       </c>
       <c r="G34">
         <v>120.6</v>
@@ -4081,28 +4081,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M34">
-        <v>30.29302304</v>
+        <v>31.23968001000001</v>
       </c>
       <c r="N34">
-        <v>48.65187491918367</v>
+        <v>47.70521794918367</v>
       </c>
       <c r="O34">
-        <v>14.5955624757551</v>
+        <v>14.3115653847551</v>
       </c>
       <c r="P34">
-        <v>34.05631244342857</v>
+        <v>33.39365256442857</v>
       </c>
       <c r="Q34">
-        <v>67.35631244342856</v>
+        <v>66.69365256442856</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1408024684456921</v>
+        <v>0.1419004364801655</v>
       </c>
       <c r="T34">
-        <v>0.9187464785839721</v>
+        <v>0.9293646686349691</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.606042251212168</v>
+        <v>2.527071273902708</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1116821924417109</v>
+        <v>0.1124413063403511</v>
       </c>
       <c r="C35">
-        <v>983.7705645945705</v>
+        <v>955.8225829280835</v>
       </c>
       <c r="D35">
-        <v>1297.658464594571</v>
+        <v>1282.876782928084</v>
       </c>
       <c r="E35">
-        <v>429.0579000000001</v>
+        <v>442.2242000000001</v>
       </c>
       <c r="F35">
-        <v>434.4879000000001</v>
+        <v>447.6542000000001</v>
       </c>
       <c r="G35">
         <v>120.6</v>
@@ -4163,45 +4163,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M35">
-        <v>31.23968001000001</v>
+        <v>33.93218836</v>
       </c>
       <c r="N35">
-        <v>47.70521794918367</v>
+        <v>45.01270959918367</v>
       </c>
       <c r="O35">
-        <v>14.3115653847551</v>
+        <v>13.5038128797551</v>
       </c>
       <c r="P35">
-        <v>33.39365256442857</v>
+        <v>31.50889671942857</v>
       </c>
       <c r="Q35">
-        <v>66.69365256442856</v>
+        <v>64.80889671942856</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1419004364801655</v>
+        <v>0.1430316762732593</v>
       </c>
       <c r="T35">
-        <v>0.9293646686349691</v>
+        <v>0.9403046220208446</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.527071273902708</v>
+        <v>2.326548972368832</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1124413063403511</v>
+        <v>0.1122995202389914</v>
       </c>
       <c r="C36">
-        <v>955.8225829280835</v>
+        <v>945.3915522491645</v>
       </c>
       <c r="D36">
-        <v>1282.876782928084</v>
+        <v>1285.612052249165</v>
       </c>
       <c r="E36">
-        <v>442.2242000000001</v>
+        <v>455.3905000000001</v>
       </c>
       <c r="F36">
-        <v>447.6542000000001</v>
+        <v>460.8205000000001</v>
       </c>
       <c r="G36">
         <v>120.6</v>
@@ -4245,28 +4245,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M36">
-        <v>33.93218836</v>
+        <v>34.93019390000001</v>
       </c>
       <c r="N36">
-        <v>45.01270959918367</v>
+        <v>44.01470405918366</v>
       </c>
       <c r="O36">
-        <v>13.5038128797551</v>
+        <v>13.2044112177551</v>
       </c>
       <c r="P36">
-        <v>31.50889671942857</v>
+        <v>30.81029284142856</v>
       </c>
       <c r="Q36">
-        <v>64.80889671942856</v>
+        <v>64.11029284142856</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1430316762732593</v>
+        <v>0.1441977234446021</v>
       </c>
       <c r="T36">
-        <v>0.9403046220208446</v>
+        <v>0.9515811893570548</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.326548972368832</v>
+        <v>2.260076144586866</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1122995202389914</v>
+        <v>0.1121577341376316</v>
       </c>
       <c r="C37">
-        <v>945.3915522491645</v>
+        <v>934.9722104314833</v>
       </c>
       <c r="D37">
-        <v>1285.612052249165</v>
+        <v>1288.359010431484</v>
       </c>
       <c r="E37">
-        <v>455.3905000000001</v>
+        <v>468.5568000000001</v>
       </c>
       <c r="F37">
-        <v>460.8205000000001</v>
+        <v>473.9868000000001</v>
       </c>
       <c r="G37">
         <v>120.6</v>
@@ -4327,28 +4327,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M37">
-        <v>34.93019390000001</v>
+        <v>35.92819944000001</v>
       </c>
       <c r="N37">
-        <v>44.01470405918366</v>
+        <v>43.01669851918367</v>
       </c>
       <c r="O37">
-        <v>13.2044112177551</v>
+        <v>12.9050095557551</v>
       </c>
       <c r="P37">
-        <v>30.81029284142856</v>
+        <v>30.11168896342857</v>
       </c>
       <c r="Q37">
-        <v>64.11029284142856</v>
+        <v>63.41168896342857</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1441977234446021</v>
+        <v>0.1454002095900494</v>
       </c>
       <c r="T37">
-        <v>0.9515811893570548</v>
+        <v>0.9632101494225217</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.260076144586866</v>
+        <v>2.197296251681675</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1121577341376316</v>
+        <v>0.1120159480362719</v>
       </c>
       <c r="C38">
-        <v>934.9722104314829</v>
+        <v>924.5646325619998</v>
       </c>
       <c r="D38">
-        <v>1288.359010431483</v>
+        <v>1291.117732562</v>
       </c>
       <c r="E38">
-        <v>468.5568</v>
+        <v>481.7231</v>
       </c>
       <c r="F38">
-        <v>473.9868</v>
+        <v>487.1531000000001</v>
       </c>
       <c r="G38">
         <v>120.6</v>
@@ -4409,28 +4409,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M38">
-        <v>35.92819944000001</v>
+        <v>36.92620498000001</v>
       </c>
       <c r="N38">
-        <v>43.01669851918367</v>
+        <v>42.01869297918367</v>
       </c>
       <c r="O38">
-        <v>12.9050095557551</v>
+        <v>12.6056078937551</v>
       </c>
       <c r="P38">
-        <v>30.11168896342857</v>
+        <v>29.41308508542857</v>
       </c>
       <c r="Q38">
-        <v>63.41168896342857</v>
+        <v>62.71308508542857</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1454002095900494</v>
+        <v>0.1466408698988442</v>
       </c>
       <c r="T38">
-        <v>0.9632101494225217</v>
+        <v>0.9752082828234</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.197296251681675</v>
+        <v>2.137909866501089</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1120159480362719</v>
+        <v>0.1118741619349121</v>
       </c>
       <c r="C39">
-        <v>924.5646325619998</v>
+        <v>914.1688943721779</v>
       </c>
       <c r="D39">
-        <v>1291.117732562</v>
+        <v>1293.888294372178</v>
       </c>
       <c r="E39">
-        <v>481.7231</v>
+        <v>494.8894</v>
       </c>
       <c r="F39">
-        <v>487.1531000000001</v>
+        <v>500.3194</v>
       </c>
       <c r="G39">
         <v>120.6</v>
@@ -4491,28 +4491,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M39">
-        <v>36.92620498000001</v>
+        <v>37.92421052</v>
       </c>
       <c r="N39">
-        <v>42.01869297918367</v>
+        <v>41.02068743918367</v>
       </c>
       <c r="O39">
-        <v>12.6056078937551</v>
+        <v>12.3062062317551</v>
       </c>
       <c r="P39">
-        <v>29.41308508542857</v>
+        <v>28.71448120742857</v>
       </c>
       <c r="Q39">
-        <v>62.71308508542857</v>
+        <v>62.01448120742857</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1466408698988442</v>
+        <v>0.1479215515079228</v>
       </c>
       <c r="T39">
-        <v>0.9752082828234</v>
+        <v>0.9875934527855972</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.137909866501089</v>
+        <v>2.081649080540535</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1118741619349121</v>
+        <v>0.1117323758335524</v>
       </c>
       <c r="C40">
-        <v>914.1688943721779</v>
+        <v>903.7850722449178</v>
       </c>
       <c r="D40">
-        <v>1293.888294372178</v>
+        <v>1296.670772244918</v>
       </c>
       <c r="E40">
-        <v>494.8894</v>
+        <v>508.0557000000001</v>
       </c>
       <c r="F40">
-        <v>500.3194</v>
+        <v>513.4857000000001</v>
       </c>
       <c r="G40">
         <v>120.6</v>
@@ -4573,28 +4573,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M40">
-        <v>37.92421052</v>
+        <v>38.92221606000001</v>
       </c>
       <c r="N40">
-        <v>41.02068743918367</v>
+        <v>40.02268189918367</v>
       </c>
       <c r="O40">
-        <v>12.3062062317551</v>
+        <v>12.0068045697551</v>
       </c>
       <c r="P40">
-        <v>28.71448120742857</v>
+        <v>28.01587732942857</v>
       </c>
       <c r="Q40">
-        <v>62.01448120742857</v>
+        <v>61.31587732942857</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1479215515079228</v>
+        <v>0.1492442226779547</v>
       </c>
       <c r="T40">
-        <v>0.9875934527855972</v>
+        <v>1.000384693894096</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.081649080540535</v>
+        <v>2.028273463090777</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1117323758335524</v>
+        <v>0.1155665897321926</v>
       </c>
       <c r="C41">
-        <v>903.7850722449178</v>
+        <v>819.3566808056405</v>
       </c>
       <c r="D41">
-        <v>1296.670772244918</v>
+        <v>1225.408680805641</v>
       </c>
       <c r="E41">
-        <v>508.0557000000001</v>
+        <v>521.2220000000001</v>
       </c>
       <c r="F41">
-        <v>513.4857000000001</v>
+        <v>526.652</v>
       </c>
       <c r="G41">
         <v>120.6</v>
@@ -4655,45 +4655,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M41">
-        <v>38.92221606000001</v>
+        <v>47.39868</v>
       </c>
       <c r="N41">
-        <v>40.02268189918367</v>
+        <v>31.54621795918368</v>
       </c>
       <c r="O41">
-        <v>12.0068045697551</v>
+        <v>9.463865387755103</v>
       </c>
       <c r="P41">
-        <v>28.01587732942857</v>
+        <v>22.08235257142858</v>
       </c>
       <c r="Q41">
-        <v>61.31587732942857</v>
+        <v>55.38235257142857</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1492442226779547</v>
+        <v>0.1506109828869877</v>
       </c>
       <c r="T41">
-        <v>1.000384693894096</v>
+        <v>1.013602309706211</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.028273463090777</v>
+        <v>1.66555055877471</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1155665897321926</v>
+        <v>0.1155242036308329</v>
       </c>
       <c r="C42">
-        <v>819.3566808056405</v>
+        <v>806.9353200641331</v>
       </c>
       <c r="D42">
-        <v>1225.408680805641</v>
+        <v>1226.153620064133</v>
       </c>
       <c r="E42">
-        <v>521.2220000000001</v>
+        <v>534.3883000000002</v>
       </c>
       <c r="F42">
-        <v>526.652</v>
+        <v>539.8183000000001</v>
       </c>
       <c r="G42">
         <v>120.6</v>
@@ -4737,28 +4737,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M42">
-        <v>47.39868</v>
+        <v>48.58364700000001</v>
       </c>
       <c r="N42">
-        <v>31.54621795918368</v>
+        <v>30.36125095918366</v>
       </c>
       <c r="O42">
-        <v>9.463865387755103</v>
+        <v>9.108375287755099</v>
       </c>
       <c r="P42">
-        <v>22.08235257142858</v>
+        <v>21.25287567142857</v>
       </c>
       <c r="Q42">
-        <v>55.38235257142857</v>
+        <v>54.55287567142857</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1506109828869877</v>
+        <v>0.1520240739505642</v>
       </c>
       <c r="T42">
-        <v>1.013602309706211</v>
+        <v>1.027267980291618</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.66555055877471</v>
+        <v>1.624927374414351</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1155242036308329</v>
+        <v>0.1154818175294731</v>
       </c>
       <c r="C43">
-        <v>806.9353200641331</v>
+        <v>794.514865586901</v>
       </c>
       <c r="D43">
-        <v>1226.153620064133</v>
+        <v>1226.899465586901</v>
       </c>
       <c r="E43">
-        <v>534.3883000000002</v>
+        <v>547.5546000000002</v>
       </c>
       <c r="F43">
-        <v>539.8183000000001</v>
+        <v>552.9846000000001</v>
       </c>
       <c r="G43">
         <v>120.6</v>
@@ -4819,28 +4819,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M43">
-        <v>48.58364700000001</v>
+        <v>49.76861400000001</v>
       </c>
       <c r="N43">
-        <v>30.36125095918366</v>
+        <v>29.17628395918367</v>
       </c>
       <c r="O43">
-        <v>9.108375287755099</v>
+        <v>8.752885187755101</v>
       </c>
       <c r="P43">
-        <v>21.25287567142857</v>
+        <v>20.42339877142857</v>
       </c>
       <c r="Q43">
-        <v>54.55287567142857</v>
+        <v>53.72339877142856</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1520240739505642</v>
+        <v>0.1534858922921951</v>
       </c>
       <c r="T43">
-        <v>1.027267980291618</v>
+        <v>1.041404880897212</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.624927374414351</v>
+        <v>1.586238627404486</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1154818175294731</v>
+        <v>0.1154394314281134</v>
       </c>
       <c r="C44">
-        <v>794.5148655869007</v>
+        <v>782.0953190287385</v>
       </c>
       <c r="D44">
-        <v>1226.899465586901</v>
+        <v>1227.646219028739</v>
       </c>
       <c r="E44">
-        <v>547.5546000000001</v>
+        <v>560.7209000000001</v>
       </c>
       <c r="F44">
-        <v>552.9846</v>
+        <v>566.1509000000001</v>
       </c>
       <c r="G44">
         <v>120.6</v>
@@ -4901,28 +4901,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M44">
-        <v>49.768614</v>
+        <v>50.95358100000001</v>
       </c>
       <c r="N44">
-        <v>29.17628395918368</v>
+        <v>27.99131695918367</v>
       </c>
       <c r="O44">
-        <v>8.752885187755103</v>
+        <v>8.3973950877551</v>
       </c>
       <c r="P44">
-        <v>20.42339877142857</v>
+        <v>19.59392187142857</v>
       </c>
       <c r="Q44">
-        <v>53.72339877142857</v>
+        <v>52.89392187142857</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1534858922921951</v>
+        <v>0.1549990025054621</v>
       </c>
       <c r="T44">
-        <v>1.041404880897212</v>
+        <v>1.056037813103002</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.586238627404486</v>
+        <v>1.54934935699973</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1154394314281134</v>
+        <v>0.1153970453267537</v>
       </c>
       <c r="C45">
-        <v>782.0953190287385</v>
+        <v>769.6766820484742</v>
       </c>
       <c r="D45">
-        <v>1227.646219028739</v>
+        <v>1228.393882048474</v>
       </c>
       <c r="E45">
-        <v>560.7209000000001</v>
+        <v>573.8872000000001</v>
       </c>
       <c r="F45">
-        <v>566.1509000000001</v>
+        <v>579.3172000000001</v>
       </c>
       <c r="G45">
         <v>120.6</v>
@@ -4983,28 +4983,28 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M45">
-        <v>50.95358100000001</v>
+        <v>52.13854800000001</v>
       </c>
       <c r="N45">
-        <v>27.99131695918367</v>
+        <v>26.80634995918367</v>
       </c>
       <c r="O45">
-        <v>8.3973950877551</v>
+        <v>8.041904987755101</v>
       </c>
       <c r="P45">
-        <v>19.59392187142857</v>
+        <v>18.76444497142857</v>
       </c>
       <c r="Q45">
-        <v>52.89392187142857</v>
+        <v>52.06444497142856</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1549990025054621</v>
+        <v>0.1565661523692029</v>
       </c>
       <c r="T45">
-        <v>1.056037813103002</v>
+        <v>1.071193350030428</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.54934935699973</v>
+        <v>1.514136871613373</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1153970453267537</v>
+        <v>0.1359675808901826</v>
       </c>
       <c r="C46">
-        <v>769.6766820484742</v>
+        <v>476.268638983945</v>
       </c>
       <c r="D46">
-        <v>1228.393882048474</v>
+        <v>948.1521389839451</v>
       </c>
       <c r="E46">
-        <v>573.8872000000001</v>
+        <v>587.0535000000001</v>
       </c>
       <c r="F46">
-        <v>579.3172000000001</v>
+        <v>592.4835</v>
       </c>
       <c r="G46">
         <v>120.6</v>
@@ -5065,45 +5065,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M46">
-        <v>52.13854800000001</v>
+        <v>86.97657780000002</v>
       </c>
       <c r="N46">
-        <v>26.80634995918367</v>
+        <v>-8.031679840816338</v>
       </c>
       <c r="O46">
-        <v>8.041904987755101</v>
+        <v>-2.409503952244901</v>
       </c>
       <c r="P46">
-        <v>18.76444497142857</v>
+        <v>-5.622175888571437</v>
       </c>
       <c r="Q46">
-        <v>52.06444497142856</v>
+        <v>27.67782411142856</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1565661523692029</v>
+        <v>0.1598100489544536</v>
       </c>
       <c r="T46">
-        <v>1.071193350030428</v>
+        <v>1.102564309262853</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.3</v>
+        <v>0.2722970940776092</v>
       </c>
       <c r="W46">
-        <v>0.063</v>
+        <v>0.106826786589407</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.514136871613373</v>
+        <v>0.9076569802586975</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1359675808901826</v>
+        <v>0.1369775808901826</v>
       </c>
       <c r="C47">
-        <v>476.268638983945</v>
+        <v>452.5993880279724</v>
       </c>
       <c r="D47">
-        <v>948.1521389839451</v>
+        <v>937.6491880279725</v>
       </c>
       <c r="E47">
-        <v>587.0535000000001</v>
+        <v>600.2198000000001</v>
       </c>
       <c r="F47">
-        <v>592.4835</v>
+        <v>605.6498</v>
       </c>
       <c r="G47">
         <v>120.6</v>
@@ -5147,37 +5147,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M47">
-        <v>86.97657780000002</v>
+        <v>88.90939064000001</v>
       </c>
       <c r="N47">
-        <v>-8.031679840816338</v>
+        <v>-9.964492680816335</v>
       </c>
       <c r="O47">
-        <v>-2.409503952244901</v>
+        <v>-2.9893478042449</v>
       </c>
       <c r="P47">
-        <v>-5.622175888571437</v>
+        <v>-6.975144876571434</v>
       </c>
       <c r="Q47">
-        <v>27.67782411142856</v>
+        <v>26.32485512342856</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1598100489544536</v>
+        <v>0.1619213461573139</v>
       </c>
       <c r="T47">
-        <v>1.102564309262853</v>
+        <v>1.122982166841795</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2722970940776092</v>
+        <v>0.2663775920324438</v>
       </c>
       <c r="W47">
-        <v>0.106826786589407</v>
+        <v>0.1076957694896373</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9076569802586975</v>
+        <v>0.8879253067748127</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1369775808901826</v>
+        <v>0.1379875808901826</v>
       </c>
       <c r="C48">
-        <v>452.5993880279724</v>
+        <v>429.1602761072821</v>
       </c>
       <c r="D48">
-        <v>937.6491880279725</v>
+        <v>927.3763761072823</v>
       </c>
       <c r="E48">
-        <v>600.2198000000001</v>
+        <v>613.3861000000002</v>
       </c>
       <c r="F48">
-        <v>605.6498</v>
+        <v>618.8161000000001</v>
       </c>
       <c r="G48">
         <v>120.6</v>
@@ -5229,37 +5229,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M48">
-        <v>88.90939064000001</v>
+        <v>90.84220348000002</v>
       </c>
       <c r="N48">
-        <v>-9.964492680816335</v>
+        <v>-11.89730552081635</v>
       </c>
       <c r="O48">
-        <v>-2.9893478042449</v>
+        <v>-3.569191656244904</v>
       </c>
       <c r="P48">
-        <v>-6.975144876571434</v>
+        <v>-8.328113864571442</v>
       </c>
       <c r="Q48">
-        <v>26.32485512342856</v>
+        <v>24.97188613542856</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1619213461573139</v>
+        <v>0.1641123149527349</v>
       </c>
       <c r="T48">
-        <v>1.122982166841795</v>
+        <v>1.144170509612395</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2663775920324438</v>
+        <v>0.260709983691328</v>
       </c>
       <c r="W48">
-        <v>0.1076957694896373</v>
+        <v>0.1085277743941131</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8879253067748127</v>
+        <v>0.8690332789710933</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1379875808901826</v>
+        <v>0.1389975808901826</v>
       </c>
       <c r="C49">
-        <v>429.1602761072821</v>
+        <v>405.9438210397163</v>
       </c>
       <c r="D49">
-        <v>927.3763761072823</v>
+        <v>917.3262210397165</v>
       </c>
       <c r="E49">
-        <v>613.3861000000002</v>
+        <v>626.5524000000001</v>
       </c>
       <c r="F49">
-        <v>618.8161000000001</v>
+        <v>631.9824000000001</v>
       </c>
       <c r="G49">
         <v>120.6</v>
@@ -5311,37 +5311,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M49">
-        <v>90.84220348000002</v>
+        <v>92.77501632000002</v>
       </c>
       <c r="N49">
-        <v>-11.89730552081635</v>
+        <v>-13.83011836081634</v>
       </c>
       <c r="O49">
-        <v>-3.569191656244904</v>
+        <v>-4.149035508244903</v>
       </c>
       <c r="P49">
-        <v>-8.328113864571442</v>
+        <v>-9.681082852571439</v>
       </c>
       <c r="Q49">
-        <v>24.97188613542856</v>
+        <v>23.61891714742856</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1641123149527349</v>
+        <v>0.166387551778749</v>
       </c>
       <c r="T49">
-        <v>1.144170509612395</v>
+        <v>1.166173788643403</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.260709983691328</v>
+        <v>0.2552785256977586</v>
       </c>
       <c r="W49">
-        <v>0.1085277743941131</v>
+        <v>0.1093251124275691</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8690332789710933</v>
+        <v>0.8509284189925288</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1389975808901826</v>
+        <v>0.1400075808901826</v>
       </c>
       <c r="C50">
-        <v>405.9438210397169</v>
+        <v>382.9428615091832</v>
       </c>
       <c r="D50">
-        <v>917.3262210397169</v>
+        <v>907.4915615091833</v>
       </c>
       <c r="E50">
-        <v>626.5524</v>
+        <v>639.7187000000001</v>
       </c>
       <c r="F50">
-        <v>631.9824</v>
+        <v>645.1487000000001</v>
       </c>
       <c r="G50">
         <v>120.6</v>
@@ -5393,37 +5393,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M50">
-        <v>92.77501632000001</v>
+        <v>94.70782916000002</v>
       </c>
       <c r="N50">
-        <v>-13.83011836081633</v>
+        <v>-15.76293120081634</v>
       </c>
       <c r="O50">
-        <v>-4.149035508244898</v>
+        <v>-4.728879360244902</v>
       </c>
       <c r="P50">
-        <v>-9.68108285257143</v>
+        <v>-11.03405184057144</v>
       </c>
       <c r="Q50">
-        <v>23.61891714742857</v>
+        <v>22.26594815942856</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.166387551778749</v>
+        <v>0.1687520135783323</v>
       </c>
       <c r="T50">
-        <v>1.166173788643403</v>
+        <v>1.189039941361901</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2552785256977587</v>
+        <v>0.2500687598671921</v>
       </c>
       <c r="W50">
-        <v>0.109325112427569</v>
+        <v>0.1100899060514962</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.850928418992529</v>
+        <v>0.8335625328906405</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1400075808901826</v>
+        <v>0.1410175808901826</v>
       </c>
       <c r="C51">
-        <v>382.9428615091832</v>
+        <v>360.150540048069</v>
       </c>
       <c r="D51">
-        <v>907.4915615091833</v>
+        <v>897.8655400480691</v>
       </c>
       <c r="E51">
-        <v>639.7187000000001</v>
+        <v>652.8850000000001</v>
       </c>
       <c r="F51">
-        <v>645.1487000000001</v>
+        <v>658.3150000000001</v>
       </c>
       <c r="G51">
         <v>120.6</v>
@@ -5475,37 +5475,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M51">
-        <v>94.70782916000002</v>
+        <v>96.64064200000001</v>
       </c>
       <c r="N51">
-        <v>-15.76293120081634</v>
+        <v>-17.69574404081634</v>
       </c>
       <c r="O51">
-        <v>-4.728879360244902</v>
+        <v>-5.3087232122449</v>
       </c>
       <c r="P51">
-        <v>-11.03405184057144</v>
+        <v>-12.38702082857144</v>
       </c>
       <c r="Q51">
-        <v>22.26594815942856</v>
+        <v>20.91297917142856</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1687520135783323</v>
+        <v>0.171211053849899</v>
       </c>
       <c r="T51">
-        <v>1.189039941361901</v>
+        <v>1.212820740189139</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2500687598671921</v>
+        <v>0.2450673846698483</v>
       </c>
       <c r="W51">
-        <v>0.1100899060514962</v>
+        <v>0.1108241079304663</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8335625328906405</v>
+        <v>0.8168912822328277</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1410175808901826</v>
+        <v>0.1420275808901826</v>
       </c>
       <c r="C52">
-        <v>360.150540048069</v>
+        <v>337.5602870913439</v>
       </c>
       <c r="D52">
-        <v>897.8655400480691</v>
+        <v>888.4415870913439</v>
       </c>
       <c r="E52">
-        <v>652.8850000000001</v>
+        <v>666.0513000000001</v>
       </c>
       <c r="F52">
-        <v>658.3150000000001</v>
+        <v>671.4813</v>
       </c>
       <c r="G52">
         <v>120.6</v>
@@ -5557,37 +5557,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M52">
-        <v>96.64064200000001</v>
+        <v>98.57345484000001</v>
       </c>
       <c r="N52">
-        <v>-17.69574404081634</v>
+        <v>-19.62855688081633</v>
       </c>
       <c r="O52">
-        <v>-5.3087232122449</v>
+        <v>-5.8885670642449</v>
       </c>
       <c r="P52">
-        <v>-12.38702082857144</v>
+        <v>-13.73998981657143</v>
       </c>
       <c r="Q52">
-        <v>20.91297917142856</v>
+        <v>19.56001018342856</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.171211053849899</v>
+        <v>0.1737704631121418</v>
       </c>
       <c r="T52">
-        <v>1.212820740189139</v>
+        <v>1.237572183866468</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2450673846698483</v>
+        <v>0.2402621418331846</v>
       </c>
       <c r="W52">
-        <v>0.1108241079304663</v>
+        <v>0.1115295175788885</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8168912822328277</v>
+        <v>0.8008738061106154</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1420275808901826</v>
+        <v>0.173472418392813</v>
       </c>
       <c r="C53">
-        <v>337.5602870913439</v>
+        <v>105.5769419664354</v>
       </c>
       <c r="D53">
-        <v>888.4415870913439</v>
+        <v>669.6245419664355</v>
       </c>
       <c r="E53">
-        <v>666.0513000000001</v>
+        <v>679.2176000000002</v>
       </c>
       <c r="F53">
-        <v>671.4813</v>
+        <v>684.6476000000001</v>
       </c>
       <c r="G53">
         <v>120.6</v>
@@ -5639,45 +5639,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M53">
-        <v>98.57345484000001</v>
+        <v>137.47723808</v>
       </c>
       <c r="N53">
-        <v>-19.62855688081633</v>
+        <v>-58.53234012081636</v>
       </c>
       <c r="O53">
-        <v>-5.8885670642449</v>
+        <v>-17.55970203624491</v>
       </c>
       <c r="P53">
-        <v>-13.73998981657143</v>
+        <v>-40.97263808457145</v>
       </c>
       <c r="Q53">
-        <v>19.56001018342856</v>
+        <v>-7.672638084571453</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1737704631121418</v>
+        <v>0.1813424258907914</v>
       </c>
       <c r="T53">
-        <v>1.237572183866468</v>
+        <v>1.310798851053859</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.2402621418331846</v>
+        <v>0.1722719318377151</v>
       </c>
       <c r="W53">
-        <v>0.1115295175788885</v>
+        <v>0.1662077960869868</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8008738061106154</v>
+        <v>0.5742397727923838</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.173472418392813</v>
+        <v>0.175022418392813</v>
       </c>
       <c r="C54">
-        <v>105.5769419664354</v>
+        <v>84.37861429695704</v>
       </c>
       <c r="D54">
-        <v>669.6245419664355</v>
+        <v>661.5925142969571</v>
       </c>
       <c r="E54">
-        <v>679.2176000000002</v>
+        <v>692.3839000000002</v>
       </c>
       <c r="F54">
-        <v>684.6476000000001</v>
+        <v>697.8139000000001</v>
       </c>
       <c r="G54">
         <v>120.6</v>
@@ -5721,37 +5721,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M54">
-        <v>137.47723808</v>
+        <v>140.12103112</v>
       </c>
       <c r="N54">
-        <v>-58.53234012081636</v>
+        <v>-61.17613316081635</v>
       </c>
       <c r="O54">
-        <v>-17.55970203624491</v>
+        <v>-18.3528399482449</v>
       </c>
       <c r="P54">
-        <v>-40.97263808457145</v>
+        <v>-42.82329321257144</v>
       </c>
       <c r="Q54">
-        <v>-7.672638084571453</v>
+        <v>-9.523293212571446</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1813424258907914</v>
+        <v>0.1842263072927232</v>
       </c>
       <c r="T54">
-        <v>1.310798851053859</v>
+        <v>1.338688188310324</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1722719318377151</v>
+        <v>0.1690215180294564</v>
       </c>
       <c r="W54">
-        <v>0.1662077960869868</v>
+        <v>0.1668604791796852</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5742397727923838</v>
+        <v>0.5634050600981879</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.175022418392813</v>
+        <v>0.176572418392813</v>
       </c>
       <c r="C55">
-        <v>84.37861429695704</v>
+        <v>63.37068828924669</v>
       </c>
       <c r="D55">
-        <v>661.5925142969571</v>
+        <v>653.7508882892467</v>
       </c>
       <c r="E55">
-        <v>692.3839000000002</v>
+        <v>705.5502000000001</v>
       </c>
       <c r="F55">
-        <v>697.8139000000001</v>
+        <v>710.9802000000001</v>
       </c>
       <c r="G55">
         <v>120.6</v>
@@ -5803,37 +5803,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M55">
-        <v>140.12103112</v>
+        <v>142.76482416</v>
       </c>
       <c r="N55">
-        <v>-61.17613316081635</v>
+        <v>-63.81992620081634</v>
       </c>
       <c r="O55">
-        <v>-18.3528399482449</v>
+        <v>-19.1459778602449</v>
       </c>
       <c r="P55">
-        <v>-42.82329321257144</v>
+        <v>-44.67394834057144</v>
       </c>
       <c r="Q55">
-        <v>-9.523293212571446</v>
+        <v>-11.37394834057145</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1842263072927232</v>
+        <v>0.187235574842565</v>
       </c>
       <c r="T55">
-        <v>1.338688188310324</v>
+        <v>1.367790105447505</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1690215180294564</v>
+        <v>0.1658914899177998</v>
       </c>
       <c r="W55">
-        <v>0.1668604791796852</v>
+        <v>0.1674889888245058</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5634050600981879</v>
+        <v>0.5529716330593326</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.176572418392813</v>
+        <v>0.178122418392813</v>
       </c>
       <c r="C56">
-        <v>63.37068828924669</v>
+        <v>42.5464729552009</v>
       </c>
       <c r="D56">
-        <v>653.7508882892467</v>
+        <v>646.092972955201</v>
       </c>
       <c r="E56">
-        <v>705.5502000000001</v>
+        <v>718.7165000000002</v>
       </c>
       <c r="F56">
-        <v>710.9802000000001</v>
+        <v>724.1465000000002</v>
       </c>
       <c r="G56">
         <v>120.6</v>
@@ -5885,37 +5885,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M56">
-        <v>142.76482416</v>
+        <v>145.4086172</v>
       </c>
       <c r="N56">
-        <v>-63.81992620081634</v>
+        <v>-66.46371924081636</v>
       </c>
       <c r="O56">
-        <v>-19.1459778602449</v>
+        <v>-19.93911577224491</v>
       </c>
       <c r="P56">
-        <v>-44.67394834057144</v>
+        <v>-46.52460346857146</v>
       </c>
       <c r="Q56">
-        <v>-11.37394834057145</v>
+        <v>-13.22460346857146</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.187235574842565</v>
+        <v>0.1903785876168442</v>
       </c>
       <c r="T56">
-        <v>1.367790105447505</v>
+        <v>1.398185441124116</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1658914899177998</v>
+        <v>0.1628752810102034</v>
       </c>
       <c r="W56">
-        <v>0.1674889888245058</v>
+        <v>0.1680946435731512</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5529716330593326</v>
+        <v>0.5429176033673446</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.178122418392813</v>
+        <v>0.1796724183928131</v>
       </c>
       <c r="C57">
-        <v>42.5464729552009</v>
+        <v>21.89958718478385</v>
       </c>
       <c r="D57">
-        <v>646.092972955201</v>
+        <v>638.612387184784</v>
       </c>
       <c r="E57">
-        <v>718.7165000000002</v>
+        <v>731.8828000000002</v>
       </c>
       <c r="F57">
-        <v>724.1465000000002</v>
+        <v>737.3128000000002</v>
       </c>
       <c r="G57">
         <v>120.6</v>
@@ -5967,37 +5967,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M57">
-        <v>145.4086172</v>
+        <v>148.05241024</v>
       </c>
       <c r="N57">
-        <v>-66.46371924081636</v>
+        <v>-69.10751228081635</v>
       </c>
       <c r="O57">
-        <v>-19.93911577224491</v>
+        <v>-20.73225368424491</v>
       </c>
       <c r="P57">
-        <v>-46.52460346857146</v>
+        <v>-48.37525859657144</v>
       </c>
       <c r="Q57">
-        <v>-13.22460346857146</v>
+        <v>-15.07525859657144</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1903785876168442</v>
+        <v>0.1936644646081361</v>
       </c>
       <c r="T57">
-        <v>1.398185441124116</v>
+        <v>1.429962382967846</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1628752810102034</v>
+        <v>0.1599667938493069</v>
       </c>
       <c r="W57">
-        <v>0.1680946435731512</v>
+        <v>0.1686786677950592</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5429176033673446</v>
+        <v>0.5332226461643564</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1796724183928131</v>
+        <v>0.181222418392813</v>
       </c>
       <c r="C58">
-        <v>21.89958718478385</v>
+        <v>1.423942012220209</v>
       </c>
       <c r="D58">
-        <v>638.612387184784</v>
+        <v>631.3030420122203</v>
       </c>
       <c r="E58">
-        <v>731.8828000000002</v>
+        <v>745.0491000000002</v>
       </c>
       <c r="F58">
-        <v>737.3128000000002</v>
+        <v>750.4791000000001</v>
       </c>
       <c r="G58">
         <v>120.6</v>
@@ -6049,37 +6049,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M58">
-        <v>148.05241024</v>
+        <v>150.69620328</v>
       </c>
       <c r="N58">
-        <v>-69.10751228081635</v>
+        <v>-71.75130532081634</v>
       </c>
       <c r="O58">
-        <v>-20.73225368424491</v>
+        <v>-21.5253915962449</v>
       </c>
       <c r="P58">
-        <v>-48.37525859657144</v>
+        <v>-50.22591372457144</v>
       </c>
       <c r="Q58">
-        <v>-15.07525859657144</v>
+        <v>-16.92591372457144</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1936644646081361</v>
+        <v>0.1971031730873951</v>
       </c>
       <c r="T58">
-        <v>1.429962382967846</v>
+        <v>1.463217322106633</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1599667938493069</v>
+        <v>0.1571603588694945</v>
       </c>
       <c r="W58">
-        <v>0.1686786677950592</v>
+        <v>0.1692421999390055</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5332226461643564</v>
+        <v>0.5238678628983151</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.181222418392813</v>
+        <v>0.182772418392813</v>
       </c>
       <c r="C59">
-        <v>1.423942012220209</v>
+        <v>-18.88627591374279</v>
       </c>
       <c r="D59">
-        <v>631.3030420122203</v>
+        <v>624.1591240862573</v>
       </c>
       <c r="E59">
-        <v>745.0491000000002</v>
+        <v>758.2154000000002</v>
       </c>
       <c r="F59">
-        <v>750.4791000000001</v>
+        <v>763.6454000000001</v>
       </c>
       <c r="G59">
         <v>120.6</v>
@@ -6131,37 +6131,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M59">
-        <v>150.69620328</v>
+        <v>153.33999632</v>
       </c>
       <c r="N59">
-        <v>-71.75130532081634</v>
+        <v>-74.39509836081636</v>
       </c>
       <c r="O59">
-        <v>-21.5253915962449</v>
+        <v>-22.31852950824491</v>
       </c>
       <c r="P59">
-        <v>-50.22591372457144</v>
+        <v>-52.07656885257146</v>
       </c>
       <c r="Q59">
-        <v>-16.92591372457144</v>
+        <v>-18.77656885257146</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1971031730873951</v>
+        <v>0.2007056295894759</v>
       </c>
       <c r="T59">
-        <v>1.463217322106633</v>
+        <v>1.498055829775838</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1571603588694945</v>
+        <v>0.1544506975096757</v>
       </c>
       <c r="W59">
-        <v>0.1692421999390055</v>
+        <v>0.1697862999400571</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5238678628983151</v>
+        <v>0.5148356583655855</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.182772418392813</v>
+        <v>0.184322418392813</v>
       </c>
       <c r="C60">
-        <v>-18.88627591374268</v>
+        <v>-39.03661974981151</v>
       </c>
       <c r="D60">
-        <v>624.1591240862573</v>
+        <v>617.1750802501884</v>
       </c>
       <c r="E60">
-        <v>758.2154</v>
+        <v>771.3817</v>
       </c>
       <c r="F60">
-        <v>763.6454</v>
+        <v>776.8117</v>
       </c>
       <c r="G60">
         <v>120.6</v>
@@ -6213,37 +6213,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M60">
-        <v>153.33999632</v>
+        <v>155.98378936</v>
       </c>
       <c r="N60">
-        <v>-74.39509836081633</v>
+        <v>-77.03889140081633</v>
       </c>
       <c r="O60">
-        <v>-22.3185295082449</v>
+        <v>-23.1116674202449</v>
       </c>
       <c r="P60">
-        <v>-52.07656885257143</v>
+        <v>-53.92722398057143</v>
       </c>
       <c r="Q60">
-        <v>-18.77656885257144</v>
+        <v>-20.62722398057143</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2007056295894759</v>
+        <v>0.2044838156770241</v>
       </c>
       <c r="T60">
-        <v>1.498055829775838</v>
+        <v>1.534593776843542</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1544506975096757</v>
+        <v>0.1518328890773083</v>
       </c>
       <c r="W60">
-        <v>0.1697862999400571</v>
+        <v>0.1703119558732765</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5148356583655855</v>
+        <v>0.5061096302576944</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.184322418392813</v>
+        <v>0.2078226237684072</v>
       </c>
       <c r="C61">
-        <v>-39.03661974981151</v>
+        <v>-141.7196847622687</v>
       </c>
       <c r="D61">
-        <v>617.1750802501884</v>
+        <v>527.6583152377314</v>
       </c>
       <c r="E61">
-        <v>771.3817</v>
+        <v>784.5480000000001</v>
       </c>
       <c r="F61">
-        <v>776.8117</v>
+        <v>789.9780000000001</v>
       </c>
       <c r="G61">
         <v>120.6</v>
@@ -6295,45 +6295,45 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M61">
-        <v>155.98378936</v>
+        <v>186.2768124</v>
       </c>
       <c r="N61">
-        <v>-77.03889140081633</v>
+        <v>-107.3319144408163</v>
       </c>
       <c r="O61">
-        <v>-23.1116674202449</v>
+        <v>-32.1995743322449</v>
       </c>
       <c r="P61">
-        <v>-53.92722398057143</v>
+        <v>-75.13234010857144</v>
       </c>
       <c r="Q61">
-        <v>-20.62722398057143</v>
+        <v>-41.83234010857144</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2044838156770241</v>
+        <v>0.210826424507935</v>
       </c>
       <c r="T61">
-        <v>1.534593776843542</v>
+        <v>1.595931651782719</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1518328890773083</v>
+        <v>0.1271412640286038</v>
       </c>
       <c r="W61">
-        <v>0.1703119558732765</v>
+        <v>0.2058200899420552</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5061096302576944</v>
+        <v>0.4238042134286794</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2078226237684072</v>
+        <v>0.2097226237684071</v>
       </c>
       <c r="C62">
-        <v>-141.7196847622687</v>
+        <v>-161.0019849573856</v>
       </c>
       <c r="D62">
-        <v>527.6583152377314</v>
+        <v>521.5423150426144</v>
       </c>
       <c r="E62">
-        <v>784.5480000000001</v>
+        <v>797.7143000000001</v>
       </c>
       <c r="F62">
-        <v>789.9780000000001</v>
+        <v>803.1443</v>
       </c>
       <c r="G62">
         <v>120.6</v>
@@ -6377,37 +6377,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M62">
-        <v>186.2768124</v>
+        <v>189.38142594</v>
       </c>
       <c r="N62">
-        <v>-107.3319144408163</v>
+        <v>-110.4365279808163</v>
       </c>
       <c r="O62">
-        <v>-32.1995743322449</v>
+        <v>-33.1309583942449</v>
       </c>
       <c r="P62">
-        <v>-75.13234010857144</v>
+        <v>-77.30556958657144</v>
       </c>
       <c r="Q62">
-        <v>-41.83234010857144</v>
+        <v>-44.00556958657144</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.210826424507935</v>
+        <v>0.2150578712901898</v>
       </c>
       <c r="T62">
-        <v>1.595931651782719</v>
+        <v>1.636852976187404</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1271412640286038</v>
+        <v>0.1250569810117415</v>
       </c>
       <c r="W62">
-        <v>0.2058200899420552</v>
+        <v>0.2063115638774314</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4238042134286794</v>
+        <v>0.4168566033724715</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2097226237684071</v>
+        <v>0.2116226237684071</v>
       </c>
       <c r="C63">
-        <v>-161.0019849573856</v>
+        <v>-180.1441305691698</v>
       </c>
       <c r="D63">
-        <v>521.5423150426144</v>
+        <v>515.5664694308302</v>
       </c>
       <c r="E63">
-        <v>797.7143000000001</v>
+        <v>810.8806000000001</v>
       </c>
       <c r="F63">
-        <v>803.1443</v>
+        <v>816.3106</v>
       </c>
       <c r="G63">
         <v>120.6</v>
@@ -6459,37 +6459,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M63">
-        <v>189.38142594</v>
+        <v>192.48603948</v>
       </c>
       <c r="N63">
-        <v>-110.4365279808163</v>
+        <v>-113.5411415208163</v>
       </c>
       <c r="O63">
-        <v>-33.1309583942449</v>
+        <v>-34.0623424562449</v>
       </c>
       <c r="P63">
-        <v>-77.30556958657144</v>
+        <v>-79.47879906457143</v>
       </c>
       <c r="Q63">
-        <v>-44.00556958657144</v>
+        <v>-46.17879906457144</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2150578712901898</v>
+        <v>0.2195120257978263</v>
       </c>
       <c r="T63">
-        <v>1.636852976187404</v>
+        <v>1.679928054508125</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1250569810117415</v>
+        <v>0.1230399329309069</v>
       </c>
       <c r="W63">
-        <v>0.2063115638774314</v>
+        <v>0.2067871838148922</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4168566033724715</v>
+        <v>0.4101331097696898</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2116226237684071</v>
+        <v>0.2135226237684071</v>
       </c>
       <c r="C64">
-        <v>-180.1441305691698</v>
+        <v>-199.1508847065388</v>
       </c>
       <c r="D64">
-        <v>515.5664694308302</v>
+        <v>509.7260152934613</v>
       </c>
       <c r="E64">
-        <v>810.8806000000001</v>
+        <v>824.0469000000002</v>
       </c>
       <c r="F64">
-        <v>816.3106</v>
+        <v>829.4769000000001</v>
       </c>
       <c r="G64">
         <v>120.6</v>
@@ -6541,37 +6541,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M64">
-        <v>192.48603948</v>
+        <v>195.59065302</v>
       </c>
       <c r="N64">
-        <v>-113.5411415208163</v>
+        <v>-116.6457550608164</v>
       </c>
       <c r="O64">
-        <v>-34.0623424562449</v>
+        <v>-34.99372651824491</v>
       </c>
       <c r="P64">
-        <v>-79.47879906457143</v>
+        <v>-81.65202854257146</v>
       </c>
       <c r="Q64">
-        <v>-46.17879906457144</v>
+        <v>-48.35202854257146</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2195120257978263</v>
+        <v>0.2242069454139838</v>
       </c>
       <c r="T64">
-        <v>1.679928054508125</v>
+        <v>1.725331515440777</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1230399329309069</v>
+        <v>0.1210869181224798</v>
       </c>
       <c r="W64">
-        <v>0.2067871838148922</v>
+        <v>0.2072477047067193</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4101331097696898</v>
+        <v>0.403623060408266</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2135226237684071</v>
+        <v>0.2154226237684071</v>
       </c>
       <c r="C65">
-        <v>-199.1508847065388</v>
+        <v>-218.0267970656773</v>
       </c>
       <c r="D65">
-        <v>509.7260152934613</v>
+        <v>504.0164029343228</v>
       </c>
       <c r="E65">
-        <v>824.0469000000002</v>
+        <v>837.2132000000001</v>
       </c>
       <c r="F65">
-        <v>829.4769000000001</v>
+        <v>842.6432000000001</v>
       </c>
       <c r="G65">
         <v>120.6</v>
@@ -6623,37 +6623,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M65">
-        <v>195.59065302</v>
+        <v>198.69526656</v>
       </c>
       <c r="N65">
-        <v>-116.6457550608164</v>
+        <v>-119.7503686008163</v>
       </c>
       <c r="O65">
-        <v>-34.99372651824491</v>
+        <v>-35.9251105802449</v>
       </c>
       <c r="P65">
-        <v>-81.65202854257146</v>
+        <v>-83.82525802057144</v>
       </c>
       <c r="Q65">
-        <v>-48.35202854257146</v>
+        <v>-50.52525802057144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2242069454139838</v>
+        <v>0.2291626938977055</v>
       </c>
       <c r="T65">
-        <v>1.725331515440777</v>
+        <v>1.773257390869688</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1210869181224798</v>
+        <v>0.1191949350268161</v>
       </c>
       <c r="W65">
-        <v>0.2072477047067193</v>
+        <v>0.2076938343206768</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.403623060408266</v>
+        <v>0.3973164500893869</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2154226237684071</v>
+        <v>0.2173226237684072</v>
       </c>
       <c r="C66">
-        <v>-218.0267970656773</v>
+        <v>-236.7762157501736</v>
       </c>
       <c r="D66">
-        <v>504.0164029343228</v>
+        <v>498.4332842498265</v>
       </c>
       <c r="E66">
-        <v>837.2132000000001</v>
+        <v>850.3795000000001</v>
       </c>
       <c r="F66">
-        <v>842.6432000000001</v>
+        <v>855.8095000000001</v>
       </c>
       <c r="G66">
         <v>120.6</v>
@@ -6705,37 +6705,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M66">
-        <v>198.69526656</v>
+        <v>201.7998801</v>
       </c>
       <c r="N66">
-        <v>-119.7503686008163</v>
+        <v>-122.8549821408163</v>
       </c>
       <c r="O66">
-        <v>-35.9251105802449</v>
+        <v>-36.8564946422449</v>
       </c>
       <c r="P66">
-        <v>-83.82525802057144</v>
+        <v>-85.99848749857145</v>
       </c>
       <c r="Q66">
-        <v>-50.52525802057144</v>
+        <v>-52.69848749857145</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2291626938977055</v>
+        <v>0.2344016280090686</v>
       </c>
       <c r="T66">
-        <v>1.773257390869688</v>
+        <v>1.823921887751679</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1191949350268161</v>
+        <v>0.1173611667956343</v>
       </c>
       <c r="W66">
-        <v>0.2076938343206768</v>
+        <v>0.2081262368695894</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3973164500893869</v>
+        <v>0.3912038893187809</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2173226237684072</v>
+        <v>0.2192226237684071</v>
       </c>
       <c r="C67">
-        <v>-236.7762157501736</v>
+        <v>-255.4032983141564</v>
       </c>
       <c r="D67">
-        <v>498.4332842498265</v>
+        <v>492.9725016858438</v>
       </c>
       <c r="E67">
-        <v>850.3795000000001</v>
+        <v>863.5458000000002</v>
       </c>
       <c r="F67">
-        <v>855.8095000000001</v>
+        <v>868.9758000000002</v>
       </c>
       <c r="G67">
         <v>120.6</v>
@@ -6787,37 +6787,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M67">
-        <v>201.7998801</v>
+        <v>204.9044936400001</v>
       </c>
       <c r="N67">
-        <v>-122.8549821408163</v>
+        <v>-125.9595956808164</v>
       </c>
       <c r="O67">
-        <v>-36.8564946422449</v>
+        <v>-37.78787870424491</v>
       </c>
       <c r="P67">
-        <v>-85.99848749857145</v>
+        <v>-88.17171697657147</v>
       </c>
       <c r="Q67">
-        <v>-52.69848749857145</v>
+        <v>-54.87171697657148</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2344016280090686</v>
+        <v>0.2399487347152176</v>
       </c>
       <c r="T67">
-        <v>1.823921887751679</v>
+        <v>1.87756664915614</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1173611667956343</v>
+        <v>0.1155829672987307</v>
       </c>
       <c r="W67">
-        <v>0.2081262368695894</v>
+        <v>0.2085455363109593</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3912038893187809</v>
+        <v>0.3852765576624357</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2192226237684071</v>
+        <v>0.2211226237684071</v>
       </c>
       <c r="C68">
-        <v>-255.4032983141564</v>
+        <v>-273.9120220873733</v>
       </c>
       <c r="D68">
-        <v>492.9725016858438</v>
+        <v>487.6300779126268</v>
       </c>
       <c r="E68">
-        <v>863.5458000000002</v>
+        <v>876.7121000000002</v>
       </c>
       <c r="F68">
-        <v>868.9758000000002</v>
+        <v>882.1421000000001</v>
       </c>
       <c r="G68">
         <v>120.6</v>
@@ -6869,37 +6869,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M68">
-        <v>204.9044936400001</v>
+        <v>208.00910718</v>
       </c>
       <c r="N68">
-        <v>-125.9595956808164</v>
+        <v>-129.0642092208163</v>
       </c>
       <c r="O68">
-        <v>-37.78787870424491</v>
+        <v>-38.7192627662449</v>
       </c>
       <c r="P68">
-        <v>-88.17171697657147</v>
+        <v>-90.34494645457144</v>
       </c>
       <c r="Q68">
-        <v>-54.87171697657148</v>
+        <v>-57.04494645457144</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2399487347152176</v>
+        <v>0.2458320297065879</v>
       </c>
       <c r="T68">
-        <v>1.87756664915614</v>
+        <v>1.934462608221478</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1155829672987307</v>
+        <v>0.1138578483838243</v>
       </c>
       <c r="W68">
-        <v>0.2085455363109593</v>
+        <v>0.2089523193510942</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3852765576624357</v>
+        <v>0.3795261612794144</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2211226237684071</v>
+        <v>0.2230226237684071</v>
       </c>
       <c r="C69">
-        <v>-273.9120220873733</v>
+        <v>-292.3061938360995</v>
       </c>
       <c r="D69">
-        <v>487.6300779126268</v>
+        <v>482.4022061639006</v>
       </c>
       <c r="E69">
-        <v>876.7121000000002</v>
+        <v>889.8784000000002</v>
       </c>
       <c r="F69">
-        <v>882.1421000000001</v>
+        <v>895.3084000000001</v>
       </c>
       <c r="G69">
         <v>120.6</v>
@@ -6951,37 +6951,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M69">
-        <v>208.00910718</v>
+        <v>211.11372072</v>
       </c>
       <c r="N69">
-        <v>-129.0642092208163</v>
+        <v>-132.1688227608163</v>
       </c>
       <c r="O69">
-        <v>-38.7192627662449</v>
+        <v>-39.6506468282449</v>
       </c>
       <c r="P69">
-        <v>-90.34494645457144</v>
+        <v>-92.51817593257144</v>
       </c>
       <c r="Q69">
-        <v>-57.04494645457144</v>
+        <v>-59.21817593257144</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2458320297065879</v>
+        <v>0.2520830306349188</v>
       </c>
       <c r="T69">
-        <v>1.934462608221478</v>
+        <v>1.994914564728399</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1138578483838243</v>
+        <v>0.1121834682605328</v>
       </c>
       <c r="W69">
-        <v>0.2089523193510942</v>
+        <v>0.2093471381841664</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3795261612794144</v>
+        <v>0.373944894201776</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2230226237684071</v>
+        <v>0.2249226237684072</v>
       </c>
       <c r="C70">
-        <v>-292.3061938360995</v>
+        <v>-310.5894588091923</v>
       </c>
       <c r="D70">
-        <v>482.4022061639006</v>
+        <v>477.2852411908078</v>
       </c>
       <c r="E70">
-        <v>889.8784000000002</v>
+        <v>903.0447000000001</v>
       </c>
       <c r="F70">
-        <v>895.3084000000001</v>
+        <v>908.4747000000001</v>
       </c>
       <c r="G70">
         <v>120.6</v>
@@ -7033,37 +7033,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M70">
-        <v>211.11372072</v>
+        <v>214.21833426</v>
       </c>
       <c r="N70">
-        <v>-132.1688227608163</v>
+        <v>-135.2734363008163</v>
       </c>
       <c r="O70">
-        <v>-39.6506468282449</v>
+        <v>-40.5820308902449</v>
       </c>
       <c r="P70">
-        <v>-92.51817593257144</v>
+        <v>-94.69140541057143</v>
       </c>
       <c r="Q70">
-        <v>-59.21817593257144</v>
+        <v>-61.39140541057144</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2520830306349188</v>
+        <v>0.2587373219457226</v>
       </c>
       <c r="T70">
-        <v>1.994914564728399</v>
+        <v>2.059266647461573</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1121834682605328</v>
+        <v>0.1105576208944381</v>
       </c>
       <c r="W70">
-        <v>0.2093471381841664</v>
+        <v>0.2097305129930915</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.373944894201776</v>
+        <v>0.3685254029814604</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2249226237684072</v>
+        <v>0.2268226237684071</v>
       </c>
       <c r="C71">
-        <v>-310.5894588091923</v>
+        <v>-328.765309214465</v>
       </c>
       <c r="D71">
-        <v>477.2852411908078</v>
+        <v>472.2756907855352</v>
       </c>
       <c r="E71">
-        <v>903.0447000000001</v>
+        <v>916.2110000000002</v>
       </c>
       <c r="F71">
-        <v>908.4747000000001</v>
+        <v>921.6410000000002</v>
       </c>
       <c r="G71">
         <v>120.6</v>
@@ -7115,37 +7115,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M71">
-        <v>214.21833426</v>
+        <v>217.3229478000001</v>
       </c>
       <c r="N71">
-        <v>-135.2734363008163</v>
+        <v>-138.3780498408164</v>
       </c>
       <c r="O71">
-        <v>-40.5820308902449</v>
+        <v>-41.51341495224492</v>
       </c>
       <c r="P71">
-        <v>-94.69140541057143</v>
+        <v>-96.86463488857149</v>
       </c>
       <c r="Q71">
-        <v>-61.39140541057144</v>
+        <v>-63.56463488857149</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2587373219457226</v>
+        <v>0.2658352326772467</v>
       </c>
       <c r="T71">
-        <v>2.059266647461573</v>
+        <v>2.127908869043626</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1105576208944381</v>
+        <v>0.1089782263102318</v>
       </c>
       <c r="W71">
-        <v>0.2097305129930915</v>
+        <v>0.2101029342360473</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3685254029814604</v>
+        <v>0.3632607543674393</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2268226237684071</v>
+        <v>0.2287226237684072</v>
       </c>
       <c r="C72">
-        <v>-328.765309214465</v>
+        <v>-346.8370921668012</v>
       </c>
       <c r="D72">
-        <v>472.2756907855352</v>
+        <v>467.3702078331989</v>
       </c>
       <c r="E72">
-        <v>916.2110000000002</v>
+        <v>929.3773000000002</v>
       </c>
       <c r="F72">
-        <v>921.6410000000002</v>
+        <v>934.8073000000002</v>
       </c>
       <c r="G72">
         <v>120.6</v>
@@ -7197,37 +7197,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M72">
-        <v>217.3229478000001</v>
+        <v>220.42756134</v>
       </c>
       <c r="N72">
-        <v>-138.3780498408164</v>
+        <v>-141.4826633808163</v>
       </c>
       <c r="O72">
-        <v>-41.51341495224492</v>
+        <v>-42.4447990142449</v>
       </c>
       <c r="P72">
-        <v>-96.86463488857149</v>
+        <v>-99.03786436657145</v>
       </c>
       <c r="Q72">
-        <v>-63.56463488857149</v>
+        <v>-65.73786436657146</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2658352326772467</v>
+        <v>0.2734226544937035</v>
       </c>
       <c r="T72">
-        <v>2.127908869043626</v>
+        <v>2.201285036941682</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1089782263102318</v>
+        <v>0.1074433217143131</v>
       </c>
       <c r="W72">
-        <v>0.2101029342360473</v>
+        <v>0.210464864739765</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3632607543674393</v>
+        <v>0.358144405714377</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2287226237684072</v>
+        <v>0.2306226237684071</v>
       </c>
       <c r="C73">
-        <v>-346.837092166801</v>
+        <v>-364.8080171460231</v>
       </c>
       <c r="D73">
-        <v>467.3702078331991</v>
+        <v>462.5655828539769</v>
       </c>
       <c r="E73">
-        <v>929.3773000000001</v>
+        <v>942.5436000000001</v>
       </c>
       <c r="F73">
-        <v>934.8073000000001</v>
+        <v>947.9736</v>
       </c>
       <c r="G73">
         <v>120.6</v>
@@ -7279,37 +7279,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M73">
-        <v>220.42756134</v>
+        <v>223.53217488</v>
       </c>
       <c r="N73">
-        <v>-141.4826633808163</v>
+        <v>-144.5872769208164</v>
       </c>
       <c r="O73">
-        <v>-42.4447990142449</v>
+        <v>-43.37618307624491</v>
       </c>
       <c r="P73">
-        <v>-99.03786436657145</v>
+        <v>-101.2110938445715</v>
       </c>
       <c r="Q73">
-        <v>-65.73786436657146</v>
+        <v>-67.91109384457145</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2734226544937035</v>
+        <v>0.2815520350113357</v>
       </c>
       <c r="T73">
-        <v>2.201285036941681</v>
+        <v>2.279902359689598</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1074433217143131</v>
+        <v>0.1059510533571698</v>
       </c>
       <c r="W73">
-        <v>0.210464864739765</v>
+        <v>0.2108167416183794</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3581444057143769</v>
+        <v>0.3531701778572328</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2306226237684071</v>
+        <v>0.2325226237684072</v>
       </c>
       <c r="C74">
-        <v>-364.8080171460231</v>
+        <v>-382.6811629994352</v>
       </c>
       <c r="D74">
-        <v>462.5655828539769</v>
+        <v>457.8587370005648</v>
       </c>
       <c r="E74">
-        <v>942.5436000000001</v>
+        <v>955.7099000000001</v>
       </c>
       <c r="F74">
-        <v>947.9736</v>
+        <v>961.1399</v>
       </c>
       <c r="G74">
         <v>120.6</v>
@@ -7361,37 +7361,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M74">
-        <v>223.53217488</v>
+        <v>226.63678842</v>
       </c>
       <c r="N74">
-        <v>-144.5872769208164</v>
+        <v>-147.6918904608164</v>
       </c>
       <c r="O74">
-        <v>-43.37618307624491</v>
+        <v>-44.30756713824491</v>
       </c>
       <c r="P74">
-        <v>-101.2110938445715</v>
+        <v>-103.3843233225714</v>
       </c>
       <c r="Q74">
-        <v>-67.91109384457145</v>
+        <v>-70.08432332257145</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2815520350113357</v>
+        <v>0.2902835918636074</v>
       </c>
       <c r="T74">
-        <v>2.279902359689598</v>
+        <v>2.36434318782625</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1059510533571698</v>
+        <v>0.1044996690646059</v>
       </c>
       <c r="W74">
-        <v>0.2108167416183794</v>
+        <v>0.211158978034566</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3531701778572328</v>
+        <v>0.3483322302153529</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2325226237684072</v>
+        <v>0.2344226237684071</v>
       </c>
       <c r="C75">
-        <v>-382.6811629994352</v>
+        <v>-400.4594845211442</v>
       </c>
       <c r="D75">
-        <v>457.8587370005648</v>
+        <v>453.2467154788559</v>
       </c>
       <c r="E75">
-        <v>955.7099000000001</v>
+        <v>968.8762000000002</v>
       </c>
       <c r="F75">
-        <v>961.1399</v>
+        <v>974.3062000000001</v>
       </c>
       <c r="G75">
         <v>120.6</v>
@@ -7443,37 +7443,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M75">
-        <v>226.63678842</v>
+        <v>229.74140196</v>
       </c>
       <c r="N75">
-        <v>-147.6918904608164</v>
+        <v>-150.7965040008164</v>
       </c>
       <c r="O75">
-        <v>-44.30756713824491</v>
+        <v>-45.23895120024491</v>
       </c>
       <c r="P75">
-        <v>-103.3843233225714</v>
+        <v>-105.5575528005714</v>
       </c>
       <c r="Q75">
-        <v>-70.08432332257145</v>
+        <v>-72.25755280057145</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2902835918636074</v>
+        <v>0.2996868069352846</v>
       </c>
       <c r="T75">
-        <v>2.36434318782625</v>
+        <v>2.455279464281106</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1044996690646059</v>
+        <v>0.1030875113745436</v>
       </c>
       <c r="W75">
-        <v>0.211158978034566</v>
+        <v>0.2114919648178826</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3483322302153529</v>
+        <v>0.3436250379151454</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2344226237684071</v>
+        <v>0.2363226237684072</v>
       </c>
       <c r="C76">
-        <v>-400.4594845211442</v>
+        <v>-418.1458186377047</v>
       </c>
       <c r="D76">
-        <v>453.2467154788559</v>
+        <v>448.7266813622954</v>
       </c>
       <c r="E76">
-        <v>968.8762000000002</v>
+        <v>982.0425000000001</v>
       </c>
       <c r="F76">
-        <v>974.3062000000001</v>
+        <v>987.4725000000001</v>
       </c>
       <c r="G76">
         <v>120.6</v>
@@ -7525,37 +7525,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M76">
-        <v>229.74140196</v>
+        <v>232.8460155</v>
       </c>
       <c r="N76">
-        <v>-150.7965040008164</v>
+        <v>-153.9011175408164</v>
       </c>
       <c r="O76">
-        <v>-45.23895120024491</v>
+        <v>-46.1703352622449</v>
       </c>
       <c r="P76">
-        <v>-105.5575528005714</v>
+        <v>-107.7307822785715</v>
       </c>
       <c r="Q76">
-        <v>-72.25755280057145</v>
+        <v>-74.43078227857146</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2996868069352846</v>
+        <v>0.309842279212696</v>
       </c>
       <c r="T76">
-        <v>2.455279464281106</v>
+        <v>2.553490642852351</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1030875113745436</v>
+        <v>0.1017130112228831</v>
       </c>
       <c r="W76">
-        <v>0.2114919648178826</v>
+        <v>0.2118160719536442</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3436250379151454</v>
+        <v>0.3390433707429434</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2363226237684072</v>
+        <v>0.2382226237684071</v>
       </c>
       <c r="C77">
-        <v>-418.1458186377047</v>
+        <v>-435.7428902272994</v>
       </c>
       <c r="D77">
-        <v>448.7266813622954</v>
+        <v>444.2959097727006</v>
       </c>
       <c r="E77">
-        <v>982.0425000000001</v>
+        <v>995.2088000000001</v>
       </c>
       <c r="F77">
-        <v>987.4725000000001</v>
+        <v>1000.6388</v>
       </c>
       <c r="G77">
         <v>120.6</v>
@@ -7607,37 +7607,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M77">
-        <v>232.8460155</v>
+        <v>235.95062904</v>
       </c>
       <c r="N77">
-        <v>-153.9011175408164</v>
+        <v>-157.0057310808164</v>
       </c>
       <c r="O77">
-        <v>-46.1703352622449</v>
+        <v>-47.1017193242449</v>
       </c>
       <c r="P77">
-        <v>-107.7307822785715</v>
+        <v>-109.9040117565715</v>
       </c>
       <c r="Q77">
-        <v>-74.43078227857146</v>
+        <v>-76.60401175657147</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.309842279212696</v>
+        <v>0.3208440408465584</v>
       </c>
       <c r="T77">
-        <v>2.553490642852351</v>
+        <v>2.659886086304532</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1017130112228831</v>
+        <v>0.1003746821278451</v>
       </c>
       <c r="W77">
-        <v>0.2118160719536442</v>
+        <v>0.2121316499542542</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3390433707429434</v>
+        <v>0.3345822737594837</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2382226237684071</v>
+        <v>0.2401226237684072</v>
       </c>
       <c r="C78">
-        <v>-435.7428902272994</v>
+        <v>-453.2533175975341</v>
       </c>
       <c r="D78">
-        <v>444.2959097727006</v>
+        <v>439.9517824024661</v>
       </c>
       <c r="E78">
-        <v>995.2088000000001</v>
+        <v>1008.3751</v>
       </c>
       <c r="F78">
-        <v>1000.6388</v>
+        <v>1013.8051</v>
       </c>
       <c r="G78">
         <v>120.6</v>
@@ -7689,37 +7689,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M78">
-        <v>235.95062904</v>
+        <v>239.0552425800001</v>
       </c>
       <c r="N78">
-        <v>-157.0057310808164</v>
+        <v>-160.1103446208164</v>
       </c>
       <c r="O78">
-        <v>-47.1017193242449</v>
+        <v>-48.03310338624491</v>
       </c>
       <c r="P78">
-        <v>-109.9040117565715</v>
+        <v>-112.0772412345715</v>
       </c>
       <c r="Q78">
-        <v>-76.60401175657147</v>
+        <v>-78.77724123457146</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3208440408465584</v>
+        <v>0.3328024774051043</v>
       </c>
       <c r="T78">
-        <v>2.659886086304532</v>
+        <v>2.775533307448207</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1003746821278451</v>
+        <v>0.09907111482748347</v>
       </c>
       <c r="W78">
-        <v>0.2121316499542542</v>
+        <v>0.2124390311236794</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3345822737594837</v>
+        <v>0.330237049424945</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2401226237684072</v>
+        <v>0.2420226237684072</v>
       </c>
       <c r="C79">
-        <v>-453.2533175975341</v>
+        <v>-470.6796176449868</v>
       </c>
       <c r="D79">
-        <v>439.9517824024661</v>
+        <v>435.6917823550133</v>
       </c>
       <c r="E79">
-        <v>1008.3751</v>
+        <v>1021.5414</v>
       </c>
       <c r="F79">
-        <v>1013.8051</v>
+        <v>1026.9714</v>
       </c>
       <c r="G79">
         <v>120.6</v>
@@ -7771,37 +7771,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M79">
-        <v>239.0552425800001</v>
+        <v>242.15985612</v>
       </c>
       <c r="N79">
-        <v>-160.1103446208164</v>
+        <v>-163.2149581608164</v>
       </c>
       <c r="O79">
-        <v>-48.03310338624491</v>
+        <v>-48.96448744824491</v>
       </c>
       <c r="P79">
-        <v>-112.0772412345715</v>
+        <v>-114.2504707125715</v>
       </c>
       <c r="Q79">
-        <v>-78.77724123457146</v>
+        <v>-80.95047071257146</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3328024774051043</v>
+        <v>0.3458480445598819</v>
       </c>
       <c r="T79">
-        <v>2.775533307448207</v>
+        <v>2.901693912332217</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09907111482748347</v>
+        <v>0.09780097232969524</v>
       </c>
       <c r="W79">
-        <v>0.2124390311236794</v>
+        <v>0.2127385307246579</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.330237049424945</v>
+        <v>0.326003241098984</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2420226237684072</v>
+        <v>0.2439226237684072</v>
       </c>
       <c r="C80">
-        <v>-470.6796176449868</v>
+        <v>-488.0242107178778</v>
       </c>
       <c r="D80">
-        <v>435.6917823550133</v>
+        <v>431.5134892821224</v>
       </c>
       <c r="E80">
-        <v>1021.5414</v>
+        <v>1034.7077</v>
       </c>
       <c r="F80">
-        <v>1026.9714</v>
+        <v>1040.1377</v>
       </c>
       <c r="G80">
         <v>120.6</v>
@@ -7853,37 +7853,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M80">
-        <v>242.15985612</v>
+        <v>245.2644696600001</v>
       </c>
       <c r="N80">
-        <v>-163.2149581608164</v>
+        <v>-166.3195717008164</v>
       </c>
       <c r="O80">
-        <v>-48.96448744824491</v>
+        <v>-49.89587151024491</v>
       </c>
       <c r="P80">
-        <v>-114.2504707125715</v>
+        <v>-116.4237001905715</v>
       </c>
       <c r="Q80">
-        <v>-80.95047071257146</v>
+        <v>-83.12370019057145</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3458480445598819</v>
+        <v>0.360136046681781</v>
       </c>
       <c r="T80">
-        <v>2.901693912332217</v>
+        <v>3.039869812919465</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09780097232969524</v>
+        <v>0.0965629853381801</v>
       </c>
       <c r="W80">
-        <v>0.2127385307246579</v>
+        <v>0.2130304480572572</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.326003241098984</v>
+        <v>0.3218766177939337</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2439226237684072</v>
+        <v>0.2458226237684071</v>
       </c>
       <c r="C81">
-        <v>-488.0242107178778</v>
+        <v>-505.2894252015977</v>
       </c>
       <c r="D81">
-        <v>431.5134892821224</v>
+        <v>427.4145747984024</v>
       </c>
       <c r="E81">
-        <v>1034.7077</v>
+        <v>1047.874</v>
       </c>
       <c r="F81">
-        <v>1040.1377</v>
+        <v>1053.304</v>
       </c>
       <c r="G81">
         <v>120.6</v>
@@ -7935,37 +7935,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M81">
-        <v>245.2644696600001</v>
+        <v>248.3690832</v>
       </c>
       <c r="N81">
-        <v>-166.3195717008164</v>
+        <v>-169.4241852408164</v>
       </c>
       <c r="O81">
-        <v>-49.89587151024491</v>
+        <v>-50.82725557224491</v>
       </c>
       <c r="P81">
-        <v>-116.4237001905715</v>
+        <v>-118.5969296685715</v>
       </c>
       <c r="Q81">
-        <v>-83.12370019057145</v>
+        <v>-85.29692966857147</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.360136046681781</v>
+        <v>0.3758528490158701</v>
       </c>
       <c r="T81">
-        <v>3.039869812919465</v>
+        <v>3.191863303565439</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0965629853381801</v>
+        <v>0.09535594802145286</v>
       </c>
       <c r="W81">
-        <v>0.2130304480572572</v>
+        <v>0.2133150674565414</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3218766177939337</v>
+        <v>0.3178531600715094</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2458226237684071</v>
+        <v>0.2477226237684071</v>
       </c>
       <c r="C82">
-        <v>-505.2894252015977</v>
+        <v>-522.4775018453502</v>
       </c>
       <c r="D82">
-        <v>427.4145747984024</v>
+        <v>423.39279815465</v>
       </c>
       <c r="E82">
-        <v>1047.874</v>
+        <v>1061.0403</v>
       </c>
       <c r="F82">
-        <v>1053.304</v>
+        <v>1066.4703</v>
       </c>
       <c r="G82">
         <v>120.6</v>
@@ -8017,37 +8017,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M82">
-        <v>248.3690832</v>
+        <v>251.4736967400001</v>
       </c>
       <c r="N82">
-        <v>-169.4241852408164</v>
+        <v>-172.5287987808164</v>
       </c>
       <c r="O82">
-        <v>-50.82725557224491</v>
+        <v>-51.75863963424491</v>
       </c>
       <c r="P82">
-        <v>-118.5969296685715</v>
+        <v>-120.7701591465715</v>
       </c>
       <c r="Q82">
-        <v>-85.29692966857147</v>
+        <v>-87.47015914657148</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3758528490158701</v>
+        <v>0.3932240515956527</v>
       </c>
       <c r="T82">
-        <v>3.191863303565439</v>
+        <v>3.359856109016251</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09535594802145286</v>
+        <v>0.09417871409526206</v>
       </c>
       <c r="W82">
-        <v>0.2133150674565414</v>
+        <v>0.2135926592163372</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3178531600715094</v>
+        <v>0.313929046984207</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2477226237684071</v>
+        <v>0.2496226237684072</v>
       </c>
       <c r="C83">
-        <v>-522.4775018453502</v>
+        <v>-539.5905978467986</v>
       </c>
       <c r="D83">
-        <v>423.39279815465</v>
+        <v>419.4460021532017</v>
       </c>
       <c r="E83">
-        <v>1061.0403</v>
+        <v>1074.2066</v>
       </c>
       <c r="F83">
-        <v>1066.4703</v>
+        <v>1079.6366</v>
       </c>
       <c r="G83">
         <v>120.6</v>
@@ -8099,37 +8099,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M83">
-        <v>251.4736967400001</v>
+        <v>254.5783102800001</v>
       </c>
       <c r="N83">
-        <v>-172.5287987808164</v>
+        <v>-175.6334123208164</v>
       </c>
       <c r="O83">
-        <v>-51.75863963424491</v>
+        <v>-52.69002369624491</v>
       </c>
       <c r="P83">
-        <v>-120.7701591465715</v>
+        <v>-122.9433886245715</v>
       </c>
       <c r="Q83">
-        <v>-87.47015914657148</v>
+        <v>-89.64338862457147</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3932240515956527</v>
+        <v>0.4125253877954112</v>
       </c>
       <c r="T83">
-        <v>3.359856109016251</v>
+        <v>3.546514781739377</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09417871409526206</v>
+        <v>0.09303019319166131</v>
       </c>
       <c r="W83">
-        <v>0.2135926592163372</v>
+        <v>0.2138634804454063</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.313929046984207</v>
+        <v>0.3101006439722044</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2496226237684072</v>
+        <v>0.2515226237684071</v>
       </c>
       <c r="C84">
-        <v>-539.5905978467986</v>
+        <v>-556.6307907103671</v>
       </c>
       <c r="D84">
-        <v>419.4460021532017</v>
+        <v>415.572109289633</v>
       </c>
       <c r="E84">
-        <v>1074.2066</v>
+        <v>1087.3729</v>
       </c>
       <c r="F84">
-        <v>1079.6366</v>
+        <v>1092.8029</v>
       </c>
       <c r="G84">
         <v>120.6</v>
@@ -8181,37 +8181,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M84">
-        <v>254.5783102800001</v>
+        <v>257.68292382</v>
       </c>
       <c r="N84">
-        <v>-175.6334123208164</v>
+        <v>-178.7380258608164</v>
       </c>
       <c r="O84">
-        <v>-52.69002369624491</v>
+        <v>-53.62140775824491</v>
       </c>
       <c r="P84">
-        <v>-122.9433886245715</v>
+        <v>-125.1166181025715</v>
       </c>
       <c r="Q84">
-        <v>-89.64338862457147</v>
+        <v>-91.81661810257147</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4125253877954112</v>
+        <v>0.4340974694304354</v>
       </c>
       <c r="T84">
-        <v>3.546514781739377</v>
+        <v>3.755133298312281</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09303019319166131</v>
+        <v>0.09190934749055697</v>
       </c>
       <c r="W84">
-        <v>0.2138634804454063</v>
+        <v>0.2141277758617267</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3101006439722044</v>
+        <v>0.3063644916351899</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2515226237684071</v>
+        <v>0.2534226237684072</v>
       </c>
       <c r="C85">
-        <v>-556.6307907103671</v>
+        <v>-573.6000818936936</v>
       </c>
       <c r="D85">
-        <v>415.572109289633</v>
+        <v>411.7691181063066</v>
       </c>
       <c r="E85">
-        <v>1087.3729</v>
+        <v>1100.5392</v>
       </c>
       <c r="F85">
-        <v>1092.8029</v>
+        <v>1105.9692</v>
       </c>
       <c r="G85">
         <v>120.6</v>
@@ -8263,37 +8263,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M85">
-        <v>257.68292382</v>
+        <v>260.78753736</v>
       </c>
       <c r="N85">
-        <v>-178.7380258608164</v>
+        <v>-181.8426394008164</v>
       </c>
       <c r="O85">
-        <v>-53.62140775824491</v>
+        <v>-54.55279182024491</v>
       </c>
       <c r="P85">
-        <v>-125.1166181025715</v>
+        <v>-127.2898475805715</v>
       </c>
       <c r="Q85">
-        <v>-91.81661810257147</v>
+        <v>-93.98984758057146</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4340974694304354</v>
+        <v>0.4583660612698377</v>
       </c>
       <c r="T85">
-        <v>3.755133298312281</v>
+        <v>3.989829129456799</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09190934749055697</v>
+        <v>0.09081518859185987</v>
       </c>
       <c r="W85">
-        <v>0.2141277758617267</v>
+        <v>0.2143857785300395</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3063644916351899</v>
+        <v>0.3027172953061995</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2534226237684071</v>
+        <v>0.2553226237684071</v>
       </c>
       <c r="C86">
-        <v>-573.6000818936932</v>
+        <v>-590.5004002556758</v>
       </c>
       <c r="D86">
-        <v>411.7691181063068</v>
+        <v>408.0350997443243</v>
       </c>
       <c r="E86">
-        <v>1100.5392</v>
+        <v>1113.7055</v>
       </c>
       <c r="F86">
-        <v>1105.9692</v>
+        <v>1119.1355</v>
       </c>
       <c r="G86">
         <v>120.6</v>
@@ -8345,37 +8345,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M86">
-        <v>260.78753736</v>
+        <v>263.8921509</v>
       </c>
       <c r="N86">
-        <v>-181.8426394008163</v>
+        <v>-184.9472529408164</v>
       </c>
       <c r="O86">
-        <v>-54.5527918202449</v>
+        <v>-55.48417588224491</v>
       </c>
       <c r="P86">
-        <v>-127.2898475805714</v>
+        <v>-129.4630770585715</v>
       </c>
       <c r="Q86">
-        <v>-93.98984758057144</v>
+        <v>-96.16307705857146</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4583660612698375</v>
+        <v>0.4858704653544934</v>
       </c>
       <c r="T86">
-        <v>3.989829129456797</v>
+        <v>4.25581773808725</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09081518859185989</v>
+        <v>0.08974677460842621</v>
       </c>
       <c r="W86">
-        <v>0.2143857785300395</v>
+        <v>0.2146377105473331</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3027172953061995</v>
+        <v>0.2991559153614206</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2553226237684071</v>
+        <v>0.2572226237684072</v>
       </c>
       <c r="C87">
-        <v>-590.5004002556758</v>
+        <v>-607.3336053186056</v>
       </c>
       <c r="D87">
-        <v>408.0350997443243</v>
+        <v>404.3681946813946</v>
       </c>
       <c r="E87">
-        <v>1113.7055</v>
+        <v>1126.8718</v>
       </c>
       <c r="F87">
-        <v>1119.1355</v>
+        <v>1132.3018</v>
       </c>
       <c r="G87">
         <v>120.6</v>
@@ -8427,37 +8427,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M87">
-        <v>263.8921509</v>
+        <v>266.99676444</v>
       </c>
       <c r="N87">
-        <v>-184.9472529408164</v>
+        <v>-188.0518664808164</v>
       </c>
       <c r="O87">
-        <v>-55.48417588224491</v>
+        <v>-56.41555994424491</v>
       </c>
       <c r="P87">
-        <v>-129.4630770585715</v>
+        <v>-131.6363065365715</v>
       </c>
       <c r="Q87">
-        <v>-96.16307705857146</v>
+        <v>-98.33630653657148</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4858704653544934</v>
+        <v>0.5173040700226714</v>
       </c>
       <c r="T87">
-        <v>4.25581773808725</v>
+        <v>4.559804719379197</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08974677460842621</v>
+        <v>0.0887032074618166</v>
       </c>
       <c r="W87">
-        <v>0.2146377105473331</v>
+        <v>0.2148837836805036</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2991559153614206</v>
+        <v>0.2956773582060553</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2572226237684072</v>
+        <v>0.2591226237684071</v>
       </c>
       <c r="C88">
-        <v>-607.3336053186056</v>
+        <v>-624.1014903559652</v>
       </c>
       <c r="D88">
-        <v>404.3681946813946</v>
+        <v>400.7666096440349</v>
       </c>
       <c r="E88">
-        <v>1126.8718</v>
+        <v>1140.0381</v>
       </c>
       <c r="F88">
-        <v>1132.3018</v>
+        <v>1145.4681</v>
       </c>
       <c r="G88">
         <v>120.6</v>
@@ -8509,37 +8509,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M88">
-        <v>266.99676444</v>
+        <v>270.10137798</v>
       </c>
       <c r="N88">
-        <v>-188.0518664808164</v>
+        <v>-191.1564800208163</v>
       </c>
       <c r="O88">
-        <v>-56.41555994424491</v>
+        <v>-57.3469440062449</v>
       </c>
       <c r="P88">
-        <v>-131.6363065365715</v>
+        <v>-133.8095360145714</v>
       </c>
       <c r="Q88">
-        <v>-98.33630653657148</v>
+        <v>-100.5095360145715</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5173040700226714</v>
+        <v>0.553573613870569</v>
       </c>
       <c r="T88">
-        <v>4.559804719379197</v>
+        <v>4.910558928562211</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0887032074618166</v>
+        <v>0.08768363036455436</v>
       </c>
       <c r="W88">
-        <v>0.2148837836805036</v>
+        <v>0.2151241999600381</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2956773582060553</v>
+        <v>0.2922787678818478</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2591226237684071</v>
+        <v>0.2610226237684071</v>
       </c>
       <c r="C89">
-        <v>-624.1014903559652</v>
+        <v>-640.8057853166765</v>
       </c>
       <c r="D89">
-        <v>400.7666096440349</v>
+        <v>397.2286146833237</v>
       </c>
       <c r="E89">
-        <v>1140.0381</v>
+        <v>1153.2044</v>
       </c>
       <c r="F89">
-        <v>1145.4681</v>
+        <v>1158.6344</v>
       </c>
       <c r="G89">
         <v>120.6</v>
@@ -8591,37 +8591,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M89">
-        <v>270.10137798</v>
+        <v>273.2059915200001</v>
       </c>
       <c r="N89">
-        <v>-191.1564800208163</v>
+        <v>-194.2610935608164</v>
       </c>
       <c r="O89">
-        <v>-57.3469440062449</v>
+        <v>-58.27832806824492</v>
       </c>
       <c r="P89">
-        <v>-133.8095360145714</v>
+        <v>-135.9827654925715</v>
       </c>
       <c r="Q89">
-        <v>-100.5095360145715</v>
+        <v>-102.6827654925715</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.553573613870569</v>
+        <v>0.5958880816931167</v>
       </c>
       <c r="T89">
-        <v>4.910558928562211</v>
+        <v>5.319772172609063</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08768363036455436</v>
+        <v>0.08668722547404804</v>
       </c>
       <c r="W89">
-        <v>0.2151241999600381</v>
+        <v>0.2153591522332195</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2922787678818478</v>
+        <v>0.2889574182468267</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2610226237684071</v>
+        <v>0.2629226237684071</v>
       </c>
       <c r="C90">
-        <v>-640.8057853166765</v>
+        <v>-657.4481595958051</v>
       </c>
       <c r="D90">
-        <v>397.2286146833237</v>
+        <v>393.7525404041949</v>
       </c>
       <c r="E90">
-        <v>1153.2044</v>
+        <v>1166.3707</v>
       </c>
       <c r="F90">
-        <v>1158.6344</v>
+        <v>1171.8007</v>
       </c>
       <c r="G90">
         <v>120.6</v>
@@ -8673,37 +8673,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M90">
-        <v>273.2059915200001</v>
+        <v>276.31060506</v>
       </c>
       <c r="N90">
-        <v>-194.2610935608164</v>
+        <v>-197.3657071008163</v>
       </c>
       <c r="O90">
-        <v>-58.27832806824492</v>
+        <v>-59.2097121302449</v>
       </c>
       <c r="P90">
-        <v>-135.9827654925715</v>
+        <v>-138.1559949705714</v>
       </c>
       <c r="Q90">
-        <v>-102.6827654925715</v>
+        <v>-104.8559949705714</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5958880816931167</v>
+        <v>0.6458960891197637</v>
       </c>
       <c r="T90">
-        <v>5.319772172609063</v>
+        <v>5.803387824664433</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08668722547404804</v>
+        <v>0.08571321170467674</v>
       </c>
       <c r="W90">
-        <v>0.2153591522332195</v>
+        <v>0.2155888246800372</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2889574182468267</v>
+        <v>0.2857107056822558</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2629226237684071</v>
+        <v>0.2648226237684072</v>
       </c>
       <c r="C91">
-        <v>-657.4481595958051</v>
+        <v>-674.0302246610572</v>
       </c>
       <c r="D91">
-        <v>393.7525404041949</v>
+        <v>390.3367753389429</v>
       </c>
       <c r="E91">
-        <v>1166.3707</v>
+        <v>1179.537</v>
       </c>
       <c r="F91">
-        <v>1171.8007</v>
+        <v>1184.967</v>
       </c>
       <c r="G91">
         <v>120.6</v>
@@ -8755,37 +8755,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M91">
-        <v>276.31060506</v>
+        <v>279.4152186000001</v>
       </c>
       <c r="N91">
-        <v>-197.3657071008163</v>
+        <v>-200.4703206408164</v>
       </c>
       <c r="O91">
-        <v>-59.2097121302449</v>
+        <v>-60.14109619224492</v>
       </c>
       <c r="P91">
-        <v>-138.1559949705714</v>
+        <v>-140.3292244485715</v>
       </c>
       <c r="Q91">
-        <v>-104.8559949705714</v>
+        <v>-107.0292244485715</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6458960891197637</v>
+        <v>0.7059056980317401</v>
       </c>
       <c r="T91">
-        <v>5.803387824664433</v>
+        <v>6.383726607130877</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08571321170467674</v>
+        <v>0.08476084268573586</v>
       </c>
       <c r="W91">
-        <v>0.2155888246800372</v>
+        <v>0.2158133932947035</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2857107056822558</v>
+        <v>0.2825361422857862</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2648226237684072</v>
+        <v>0.2667226237684072</v>
       </c>
       <c r="C92">
-        <v>-674.0302246610572</v>
+        <v>-690.5535365437402</v>
       </c>
       <c r="D92">
-        <v>390.3367753389429</v>
+        <v>386.97976345626</v>
       </c>
       <c r="E92">
-        <v>1179.537</v>
+        <v>1192.7033</v>
       </c>
       <c r="F92">
-        <v>1184.967</v>
+        <v>1198.1333</v>
       </c>
       <c r="G92">
         <v>120.6</v>
@@ -8837,37 +8837,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M92">
-        <v>279.4152186000001</v>
+        <v>282.5198321400001</v>
       </c>
       <c r="N92">
-        <v>-200.4703206408164</v>
+        <v>-203.5749341808164</v>
       </c>
       <c r="O92">
-        <v>-60.14109619224492</v>
+        <v>-61.07248025424492</v>
       </c>
       <c r="P92">
-        <v>-140.3292244485715</v>
+        <v>-142.5024539265715</v>
       </c>
       <c r="Q92">
-        <v>-107.0292244485715</v>
+        <v>-109.2024539265715</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7059056980317401</v>
+        <v>0.7792507755908223</v>
       </c>
       <c r="T92">
-        <v>6.383726607130877</v>
+        <v>7.093029563478753</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08476084268573586</v>
+        <v>0.08382940485402447</v>
       </c>
       <c r="W92">
-        <v>0.2158133932947035</v>
+        <v>0.216033026335421</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2825361422857862</v>
+        <v>0.2794313495134149</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2667226237684072</v>
+        <v>0.2686226237684072</v>
       </c>
       <c r="C93">
-        <v>-690.5535365437402</v>
+        <v>-707.0195982022829</v>
       </c>
       <c r="D93">
-        <v>386.97976345626</v>
+        <v>383.6800017977172</v>
       </c>
       <c r="E93">
-        <v>1192.7033</v>
+        <v>1205.8696</v>
       </c>
       <c r="F93">
-        <v>1198.1333</v>
+        <v>1211.2996</v>
       </c>
       <c r="G93">
         <v>120.6</v>
@@ -8919,37 +8919,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M93">
-        <v>282.5198321400001</v>
+        <v>285.62444568</v>
       </c>
       <c r="N93">
-        <v>-203.5749341808164</v>
+        <v>-206.6795477208163</v>
       </c>
       <c r="O93">
-        <v>-61.07248025424492</v>
+        <v>-62.0038643162449</v>
       </c>
       <c r="P93">
-        <v>-142.5024539265715</v>
+        <v>-144.6756834045714</v>
       </c>
       <c r="Q93">
-        <v>-109.2024539265715</v>
+        <v>-111.3756834045714</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7792507755908223</v>
+        <v>0.8709321225396753</v>
       </c>
       <c r="T93">
-        <v>7.093029563478753</v>
+        <v>7.979658258913599</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08382940485402447</v>
+        <v>0.08291821567082858</v>
       </c>
       <c r="W93">
-        <v>0.216033026335421</v>
+        <v>0.2162478847448186</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2794313495134149</v>
+        <v>0.2763940522360953</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2686226237684072</v>
+        <v>0.2705226237684071</v>
       </c>
       <c r="C94">
-        <v>-707.0195982022829</v>
+        <v>-723.4298617658577</v>
       </c>
       <c r="D94">
-        <v>383.6800017977172</v>
+        <v>380.4360382341425</v>
       </c>
       <c r="E94">
-        <v>1205.8696</v>
+        <v>1219.0359</v>
       </c>
       <c r="F94">
-        <v>1211.2996</v>
+        <v>1224.4659</v>
       </c>
       <c r="G94">
         <v>120.6</v>
@@ -9001,37 +9001,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M94">
-        <v>285.62444568</v>
+        <v>288.7290592200001</v>
       </c>
       <c r="N94">
-        <v>-206.6795477208163</v>
+        <v>-209.7841612608164</v>
       </c>
       <c r="O94">
-        <v>-62.0038643162449</v>
+        <v>-62.93524837824492</v>
       </c>
       <c r="P94">
-        <v>-144.6756834045714</v>
+        <v>-146.8489128825715</v>
       </c>
       <c r="Q94">
-        <v>-111.3756834045714</v>
+        <v>-113.5489128825715</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8709321225396753</v>
+        <v>0.9888081400453433</v>
       </c>
       <c r="T94">
-        <v>7.979658258913599</v>
+        <v>9.119609438758399</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08291821567082858</v>
+        <v>0.08202662195393794</v>
       </c>
       <c r="W94">
-        <v>0.2162478847448186</v>
+        <v>0.2164581225432614</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2763940522360953</v>
+        <v>0.2734220731797931</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2705226237684071</v>
+        <v>0.2724226237684071</v>
       </c>
       <c r="C95">
-        <v>-723.4298617658577</v>
+        <v>-739.7857306651375</v>
       </c>
       <c r="D95">
-        <v>380.4360382341425</v>
+        <v>377.2464693348628</v>
       </c>
       <c r="E95">
-        <v>1219.0359</v>
+        <v>1232.2022</v>
       </c>
       <c r="F95">
-        <v>1224.4659</v>
+        <v>1237.6322</v>
       </c>
       <c r="G95">
         <v>120.6</v>
@@ -9083,37 +9083,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M95">
-        <v>288.7290592200001</v>
+        <v>291.8336727600001</v>
       </c>
       <c r="N95">
-        <v>-209.7841612608164</v>
+        <v>-212.8887748008164</v>
       </c>
       <c r="O95">
-        <v>-62.93524837824492</v>
+        <v>-63.86663244024492</v>
       </c>
       <c r="P95">
-        <v>-146.8489128825715</v>
+        <v>-149.0221423605715</v>
       </c>
       <c r="Q95">
-        <v>-113.5489128825715</v>
+        <v>-115.7221423605715</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9888081400453433</v>
+        <v>1.145976163386234</v>
       </c>
       <c r="T95">
-        <v>9.119609438758399</v>
+        <v>10.63954434521814</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08202662195393794</v>
+        <v>0.08115399831613009</v>
       </c>
       <c r="W95">
-        <v>0.2164581225432614</v>
+        <v>0.2166638871970565</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2734220731797931</v>
+        <v>0.2705133277204336</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2724226237684071</v>
+        <v>0.2743226237684072</v>
       </c>
       <c r="C96">
-        <v>-739.7857306651375</v>
+        <v>-756.0885616567589</v>
       </c>
       <c r="D96">
-        <v>377.2464693348628</v>
+        <v>374.1099383432412</v>
       </c>
       <c r="E96">
-        <v>1232.2022</v>
+        <v>1245.3685</v>
       </c>
       <c r="F96">
-        <v>1237.6322</v>
+        <v>1250.7985</v>
       </c>
       <c r="G96">
         <v>120.6</v>
@@ -9165,37 +9165,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M96">
-        <v>291.8336727600001</v>
+        <v>294.9382863</v>
       </c>
       <c r="N96">
-        <v>-212.8887748008164</v>
+        <v>-215.9933883408164</v>
       </c>
       <c r="O96">
-        <v>-63.86663244024492</v>
+        <v>-64.79801650224491</v>
       </c>
       <c r="P96">
-        <v>-149.0221423605715</v>
+        <v>-151.1953718385714</v>
       </c>
       <c r="Q96">
-        <v>-115.7221423605715</v>
+        <v>-117.8953718385714</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.145976163386234</v>
+        <v>1.366011396063482</v>
       </c>
       <c r="T96">
-        <v>10.63954434521814</v>
+        <v>12.76745321426177</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08115399831613009</v>
+        <v>0.0802997457022761</v>
       </c>
       <c r="W96">
-        <v>0.2166638871970565</v>
+        <v>0.2168653199634033</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2705133277204336</v>
+        <v>0.2676658190075869</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2743226237684072</v>
+        <v>0.2762226237684072</v>
       </c>
       <c r="C97">
-        <v>-756.0885616567589</v>
+        <v>-772.3396667476279</v>
       </c>
       <c r="D97">
-        <v>374.1099383432412</v>
+        <v>371.0251332523723</v>
       </c>
       <c r="E97">
-        <v>1245.3685</v>
+        <v>1258.5348</v>
       </c>
       <c r="F97">
-        <v>1250.7985</v>
+        <v>1263.9648</v>
       </c>
       <c r="G97">
         <v>120.6</v>
@@ -9247,37 +9247,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M97">
-        <v>294.9382863</v>
+        <v>298.0428998400001</v>
       </c>
       <c r="N97">
-        <v>-215.9933883408164</v>
+        <v>-219.0980018808164</v>
       </c>
       <c r="O97">
-        <v>-64.79801650224491</v>
+        <v>-65.72940056424493</v>
       </c>
       <c r="P97">
-        <v>-151.1953718385714</v>
+        <v>-153.3686013165715</v>
       </c>
       <c r="Q97">
-        <v>-117.8953718385714</v>
+        <v>-120.0686013165715</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.366011396063482</v>
+        <v>1.696064245079353</v>
       </c>
       <c r="T97">
-        <v>12.76745321426177</v>
+        <v>15.95931651782722</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0802997457022761</v>
+        <v>0.07946329001787737</v>
       </c>
       <c r="W97">
-        <v>0.2168653199634033</v>
+        <v>0.2170625562137845</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2676658190075869</v>
+        <v>0.2648776333929245</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2762226237684072</v>
+        <v>0.2781226237684071</v>
       </c>
       <c r="C98">
-        <v>-772.3396667476277</v>
+        <v>-788.5403150247986</v>
       </c>
       <c r="D98">
-        <v>371.0251332523723</v>
+        <v>367.9907849752015</v>
       </c>
       <c r="E98">
-        <v>1258.5348</v>
+        <v>1271.7011</v>
       </c>
       <c r="F98">
-        <v>1263.9648</v>
+        <v>1277.1311</v>
       </c>
       <c r="G98">
         <v>120.6</v>
@@ -9329,37 +9329,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M98">
-        <v>298.04289984</v>
+        <v>301.14751338</v>
       </c>
       <c r="N98">
-        <v>-219.0980018808164</v>
+        <v>-222.2026154208164</v>
       </c>
       <c r="O98">
-        <v>-65.7294005642449</v>
+        <v>-66.6607846262449</v>
       </c>
       <c r="P98">
-        <v>-153.3686013165715</v>
+        <v>-155.5418307945715</v>
       </c>
       <c r="Q98">
-        <v>-120.0686013165715</v>
+        <v>-122.2418307945715</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.696064245079349</v>
+        <v>2.246152326772465</v>
       </c>
       <c r="T98">
-        <v>15.95931651782718</v>
+        <v>21.27908869043624</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07946329001787739</v>
+        <v>0.07864408084243535</v>
       </c>
       <c r="W98">
-        <v>0.2170625562137845</v>
+        <v>0.2172557257373537</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2648776333929246</v>
+        <v>0.2621469361414511</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2781226237684071</v>
+        <v>0.2800226237684071</v>
       </c>
       <c r="C99">
-        <v>-788.5403150247986</v>
+        <v>-804.6917343962913</v>
       </c>
       <c r="D99">
-        <v>367.9907849752015</v>
+        <v>365.0056656037088</v>
       </c>
       <c r="E99">
-        <v>1271.7011</v>
+        <v>1284.8674</v>
       </c>
       <c r="F99">
-        <v>1277.1311</v>
+        <v>1290.2974</v>
       </c>
       <c r="G99">
         <v>120.6</v>
@@ -9411,37 +9411,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M99">
-        <v>301.14751338</v>
+        <v>304.25212692</v>
       </c>
       <c r="N99">
-        <v>-222.2026154208164</v>
+        <v>-225.3072289608164</v>
       </c>
       <c r="O99">
-        <v>-66.6607846262449</v>
+        <v>-67.59216868824491</v>
       </c>
       <c r="P99">
-        <v>-155.5418307945715</v>
+        <v>-157.7150602725715</v>
       </c>
       <c r="Q99">
-        <v>-122.2418307945715</v>
+        <v>-124.4150602725715</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.246152326772465</v>
+        <v>3.346328490158697</v>
       </c>
       <c r="T99">
-        <v>21.27908869043624</v>
+        <v>31.91863303565435</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07864408084243535</v>
+        <v>0.07784159022159418</v>
       </c>
       <c r="W99">
-        <v>0.2172557257373537</v>
+        <v>0.2174449530257481</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2621469361414511</v>
+        <v>0.2594719674053139</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2800226237684071</v>
+        <v>0.2819226237684072</v>
       </c>
       <c r="C100">
-        <v>-804.6917343962913</v>
+        <v>-820.7951132478596</v>
       </c>
       <c r="D100">
-        <v>365.0056656037088</v>
+        <v>362.0685867521404</v>
       </c>
       <c r="E100">
-        <v>1284.8674</v>
+        <v>1298.0337</v>
       </c>
       <c r="F100">
-        <v>1290.2974</v>
+        <v>1303.4637</v>
       </c>
       <c r="G100">
         <v>120.6</v>
@@ -9493,37 +9493,37 @@
         <v>78.94489795918368</v>
       </c>
       <c r="M100">
-        <v>304.25212692</v>
+        <v>307.35674046</v>
       </c>
       <c r="N100">
-        <v>-225.3072289608164</v>
+        <v>-228.4118425008164</v>
       </c>
       <c r="O100">
-        <v>-67.59216868824491</v>
+        <v>-68.5235527502449</v>
       </c>
       <c r="P100">
-        <v>-157.7150602725715</v>
+        <v>-159.8882897505715</v>
       </c>
       <c r="Q100">
-        <v>-124.4150602725715</v>
+        <v>-126.5882897505715</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.346328490158697</v>
+        <v>6.646856980317394</v>
       </c>
       <c r="T100">
-        <v>31.91863303565435</v>
+        <v>63.8372660713087</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07784159022159418</v>
+        <v>0.07705531153248717</v>
       </c>
       <c r="W100">
-        <v>0.2174449530257481</v>
+        <v>0.2176303575406396</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2594719674053139</v>
+        <v>0.2568510384416238</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2819226237684072</v>
-      </c>
-      <c r="C101">
-        <v>-820.7951132478596</v>
-      </c>
-      <c r="D101">
-        <v>362.0685867521404</v>
-      </c>
-      <c r="E101">
-        <v>1298.0337</v>
-      </c>
-      <c r="F101">
-        <v>1303.4637</v>
-      </c>
-      <c r="G101">
-        <v>120.6</v>
-      </c>
-      <c r="H101">
-        <v>1311.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>112.2448979591837</v>
-      </c>
-      <c r="K101">
-        <v>33.3</v>
-      </c>
-      <c r="L101">
-        <v>78.94489795918368</v>
-      </c>
-      <c r="M101">
-        <v>307.35674046</v>
-      </c>
-      <c r="N101">
-        <v>-228.4118425008164</v>
-      </c>
-      <c r="O101">
-        <v>-68.5235527502449</v>
-      </c>
-      <c r="P101">
-        <v>-159.8882897505715</v>
-      </c>
-      <c r="Q101">
-        <v>-126.5882897505715</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.646856980317394</v>
-      </c>
-      <c r="T101">
-        <v>63.8372660713087</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07705531153248717</v>
-      </c>
-      <c r="W101">
-        <v>0.2176303575406396</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2568510384416238</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
